--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3990,29 +3990,23 @@
           <t>한국자산관리공사</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>70</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486796</v>
+        <v>21160</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4620,29 +4614,23 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>93</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649841</v>
+        <v>25146</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(주)강원랜드</t>
+          <t>(주)공영홈쇼핑</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -547,61 +547,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>(주)한국가스기술공사</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1024&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151757</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18889</v>
+        <v>31176</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+          <t>88관광개발(주)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>31176</v>
+        <v>18886</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
+          <t>가덕도신공항건설공단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -616,18 +616,18 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18886</v>
+        <v>18889</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>가덕도신공항건설공단</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -642,7 +642,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -653,33 +653,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>강원대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>18889</v>
+        <v>27742</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강원대학교치과병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -696,18 +698,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27742</v>
+        <v>28132</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>경북대학교병원</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -724,132 +726,130 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>28132</v>
+        <v>27748</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+          <t>경북대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27748</v>
+        <v>18885</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경북대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>공무원연금공단</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(주)상록골프앤리조트</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>18885</v>
+        <v>28717</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
+          <t>국가철도공단</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(주)상록골프앤리조트</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>28717</v>
+        <v>60742</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국가철도공단</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+          <t>국립농업박물관</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>60742</v>
+        <v>18890</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -864,18 +864,18 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>18890</v>
+        <v>18888</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국민건강보험공단 일산병원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -890,18 +890,18 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18888</v>
+        <v>18923</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국민건강보험공단 일산병원</t>
+          <t>국민연금공단</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -916,104 +916,110 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>18923</v>
+        <v>19350</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국민연금공단</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>국방과학연구소</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>19350</v>
+        <v>32627</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32627</v>
+        <v>28199</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>아리랑TV미디어</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>28199</v>
+        <v>32026</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1029,208 +1035,208 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>아리랑TV미디어</t>
+          <t>지케이엘위드주식회사</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>32026</v>
+        <v>29463</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>극지연구소</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>지케이엘위드주식회사</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>29463</v>
+        <v>27696</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>극지연구소</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>27696</v>
+        <v>172596</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>35</v>
-      </c>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>172596</v>
+        <v>18905</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>대구경북첨단의료산업진흥재단</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>주식회사 메디밸리파트너스</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>18905</v>
+        <v>27790</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>주식회사 메디밸리파트너스</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>27790</v>
+        <v>30071</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>30071</v>
+        <v>32440</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1239,30 +1245,30 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+          <t>(주)한빛씨에스</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>32440</v>
+        <v>30983</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>독립기념관</t>
+          <t>부산항만공사</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1271,81 +1277,81 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(주)한빛씨에스</t>
+          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>30983</v>
+        <v>54782</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3</v>
-      </c>
+          <t>북한이탈주민지원재단</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>54782</v>
+        <v>18890</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>분당서울대학교병원</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>이지케어텍</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>18890</v>
+        <v>35065</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1361,90 +1367,90 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>이지케어텍</t>
+          <t>티피에스주식회사</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>35065</v>
+        <v>30950</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>티피에스주식회사</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>30950</v>
+        <v>27730</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>(주)국민행복기금</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>27730</v>
+        <v>27691</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1453,113 +1459,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(주)국민행복기금</t>
+          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>27691</v>
+        <v>37764</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2</v>
-      </c>
+          <t>서울대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>37764</v>
+        <v>18896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>서울올림픽기념국민체육진흥공단</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>18896</v>
+        <v>50216</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50216</v>
+        <v>38439</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1576,137 +1578,141 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>38439</v>
+        <v>29493</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+          <t>식품안전정보원</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>29493</v>
+        <v>18887</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>신용보증기금</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>38</v>
+      </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>18887</v>
+        <v>165900</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>38</v>
-      </c>
+          <t>에너지경제연구원</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>165900</v>
+        <v>18891</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>여수광양항만공사</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>18891</v>
+        <v>32666</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>연구개발특구진흥재단</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1715,30 +1721,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+          <t>(주)연구개발특구에프엔에스</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>32666</v>
+        <v>45372</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>연구개발특구진흥재단</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1747,30 +1753,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(주)연구개발특구에프엔에스</t>
+          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>45372</v>
+        <v>58855</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1779,23 +1785,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
+          <t>케이바이오스타트</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58855</v>
+        <v>27693</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1811,30 +1817,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>케이바이오스타트</t>
+          <t>울산항만관리(주)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>27693</v>
+        <v>35740</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1843,30 +1849,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>울산항만관리(주)</t>
+          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>35740</v>
+        <v>52270</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>인천항만공사</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1875,55 +1881,49 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
+          <t>인천항보안공사</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>52270</v>
+        <v>29461</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
+          <t>재단법인 대한건설기계안전관리원</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>인천항보안공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>29461</v>
+        <v>18916</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1938,158 +1938,164 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>18916</v>
+        <v>18900</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>정보통신기획평가원</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>18900</v>
+        <v>25444</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+          <t>정보통신정책연구원</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>25444</v>
+        <v>18886</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>제주국제자유도시개발센터</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>18886</v>
+        <v>43079</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>주식회사 에스알</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>43079</v>
+        <v>28132</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>주식회사 에스알</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>28132</v>
+        <v>220529</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>중소기업은행</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2105,30 +2111,30 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>220529</v>
+        <v>253988</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>중소기업은행</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2137,113 +2143,109 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
+          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>253988</v>
+        <v>79797</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>5</v>
-      </c>
+          <t>충남대학교병원</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>79797</v>
+        <v>18892</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>코레일네트웍스(주)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>(주)케이아이비보험중개</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>18892</v>
+        <v>39613</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>코레일유통(주)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(주)케이아이비보험중개</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>39613</v>
+        <v>59335</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코레일유통(주)</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2260,53 +2262,57 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>59335</v>
+        <v>29359</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>태권도원운영관리(주)</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>29359</v>
+        <v>27789</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2315,116 +2321,116 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>태권도원운영관리(주)</t>
+          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>27789</v>
+        <v>125892</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>한국개발연구원</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>125892</v>
+        <v>27744</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>한국개발연구원</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+          <t>한국고용정보원</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>27744</v>
+        <v>18880</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>한국공항공사</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>18880</v>
+        <v>44936</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2433,143 +2439,143 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>44936</v>
+        <v>41895</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>41895</v>
+        <v>27699</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국관세정보원</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>27699</v>
+        <v>88687</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>88687</v>
+        <v>28118</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>(주)코웍스</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>28118</v>
+        <v>29463</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2585,30 +2591,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(주)코웍스</t>
+          <t>엘엑스파트너스(주)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>29463</v>
+        <v>33174</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2617,30 +2623,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>엘엑스파트너스(주)</t>
+          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>33174</v>
+        <v>134226</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2649,88 +2655,88 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
+          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>134226</v>
+        <v>143254</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>9</v>
-      </c>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>143254</v>
+        <v>18902</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>한국농수산식품유통공사</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>에이플(주) | 칭다오aT물류유한공사</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>18902</v>
+        <v>40884</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국농어촌공사</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2739,30 +2745,30 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>에이플(주) | 칭다오aT물류유한공사</t>
+          <t>KRCThailand. Co.Ltd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>40884</v>
+        <v>43161</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2771,30 +2777,30 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KRCThailand. Co.Ltd</t>
+          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>43161</v>
+        <v>59119</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2803,30 +2809,30 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
+          <t>도로교통안전관리주식회사</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>59119</v>
+        <v>35352</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2835,30 +2841,30 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>도로교통안전관리주식회사</t>
+          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>35352</v>
+        <v>120830</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국디자인진흥원</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2867,81 +2873,81 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
+          <t>베이징KIDP산업디자인서비스유한공사</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>120830</v>
+        <v>28660</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>베이징KIDP산업디자인서비스유한공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>28660</v>
+        <v>18898</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>한국마사회</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한국마사회시설관리(주)</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>18898</v>
+        <v>33120</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국마사회</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2957,23 +2963,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한국마사회시설관리(주)</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>33120</v>
+        <v>54973</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2989,23 +2995,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>54973</v>
+        <v>29388</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3021,90 +3027,90 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>코바코파트너스주식회사</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29388</v>
+        <v>29943</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>코바코파트너스주식회사</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>29943</v>
+        <v>40110</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>40110</v>
+        <v>44774</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3113,90 +3119,90 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+          <t>코리아메디컬홀딩스</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>44774</v>
+        <v>27747</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>코리아메디컬홀딩스</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>27747</v>
+        <v>28487</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>알이비파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>28487</v>
+        <v>37300</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3205,266 +3211,266 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>알이비파트너스주식회사</t>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>37300</v>
+        <v>284521</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>39</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>284521</v>
+        <v>18897</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>한국산림복지진흥원</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(주)포이파트너스</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>18897</v>
+        <v>33084</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>(주)포이파트너스</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>33084</v>
+        <v>25486</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>KTLChinaCo.,Ltd</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>25486</v>
+        <v>29430</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>KTLChinaCo.,Ltd</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>29430</v>
+        <v>95626</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(주)키콕스파트너스</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>95626</v>
+        <v>45150</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>(주)키콕스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>45150</v>
+        <v>18916</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>한국서부발전(주)</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>9</v>
+      </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>18916</v>
+        <v>136049</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국석유공사</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C103" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3473,148 +3479,148 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026090303237272</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>251314</v>
+        <v>110550</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국세라믹기술원</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>136049</v>
+        <v>58849</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>14</v>
-      </c>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>110550</v>
+        <v>18896</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>58849</v>
+        <v>142356</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>한국수자원공사</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>12</v>
+      </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>18896</v>
+        <v>99981</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3623,87 +3629,79 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>142356</v>
+        <v>88925</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>99981</v>
+        <v>29355</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>88925</v>
+        <v>30080</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국에너지기술평가원</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3720,18 +3718,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>29355</v>
+        <v>28175</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3748,46 +3746,44 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30080</v>
+        <v>25674</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>28175</v>
+        <v>18925</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국원산지정보원</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3804,158 +3800,168 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>25674</v>
+        <v>27746</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>한국원자력안전기술원</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>18925</v>
+        <v>28110</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>27746</v>
+        <v>18896</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
+          <t>한국원자력의학원</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>28110</v>
+        <v>31846</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>KOFPI.PARAGUAY.S.A</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>18896</v>
+        <v>29406</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>31846</v>
+        <v>486796</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3971,113 +3977,107 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
+          <t>한국잡월드파트너즈(주)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29406</v>
+        <v>29539</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>70</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486796</v>
+        <v>18883</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전기안전공사</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>한국잡월드파트너즈(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>29539</v>
+        <v>18891</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>케이피엑스서비스원주식회사</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>18883</v>
+        <v>28108</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국전력공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>18891</v>
+        <v>34716</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4119,49 +4119,55 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>케이피엑스서비스원주식회사</t>
+          <t>한전기술서비스(주)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>28108</v>
+        <v>45469</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>한국조폐공사</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>34716</v>
+        <v>36852</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4177,30 +4183,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>45469</v>
+        <v>30022</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4209,30 +4215,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>36852</v>
+        <v>179646</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4241,30 +4247,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>30022</v>
+        <v>40148</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4273,62 +4279,56 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>179646</v>
+        <v>47665</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>2</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>40148</v>
+        <v>18899</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4337,176 +4337,176 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>47665</v>
+        <v>105871</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>한국청소년활동진흥원</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>키와파트너스㈜</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>18899</v>
+        <v>30150</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>105871</v>
+        <v>27769</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국탄소산업진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157896</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>30150</v>
+        <v>75106</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>27769</v>
+        <v>137010</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>18</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157896</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>75106</v>
+        <v>18884</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>한국특허기술진흥원</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4515,56 +4515,58 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+          <t>IPKoreaCenterInc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>137010</v>
+        <v>29482</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>한국해양과학기술원</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18884</v>
+        <v>47713</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4573,176 +4575,176 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>IPKoreaCenterInc</t>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>29482</v>
+        <v>649841</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>한국해외인프라도시개발지원공사</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KINDUSALLC</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>47713</v>
+        <v>67551</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649841</v>
+        <v>74983</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>67551</v>
+        <v>18900</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국환경산업기술원</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>74983</v>
+        <v>29949</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>한전KDN</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>18900</v>
+        <v>25429</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4751,190 +4753,130 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>북경한능환보기술자문유한공사</t>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>29949</v>
+        <v>40050</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한전원자력연료주식회사</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>25429</v>
+        <v>32943</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>3</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>40050</v>
+        <v>18897</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>2</v>
-      </c>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>32943</v>
+        <v>18898</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>18897</v>
+        <v>40376</v>
       </c>
       <c r="H150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
-        <v>18898</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>40376</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
+          <t>(주)강원랜드</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -547,61 +547,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+          <t>(주)공영홈쇼핑</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1024&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151757</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>31176</v>
+        <v>18889</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>(주)한국가스기술공사</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18886</v>
+        <v>31176</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가덕도신공항건설공단</t>
+          <t>88관광개발(주)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -616,18 +616,18 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18889</v>
+        <v>18886</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
+          <t>가덕도신공항건설공단</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -642,7 +642,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -653,35 +653,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강원대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+          <t>가축위생방역지원본부</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27742</v>
+        <v>18889</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>강원대학교치과병원</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -698,18 +696,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>28132</v>
+        <v>27742</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -726,130 +724,132 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>27748</v>
+        <v>28132</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>경북대학교병원</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>18885</v>
+        <v>27748</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+          <t>경북대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(주)상록골프앤리조트</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>28717</v>
+        <v>18885</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>국가철도공단</t>
+          <t>공무원연금공단</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(주)상록골프앤리조트</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>60742</v>
+        <v>28717</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>국가철도공단</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>18890</v>
+        <v>60742</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국립농업박물관</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -864,18 +864,18 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>18888</v>
+        <v>18890</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>국민건강보험공단 일산병원</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -890,18 +890,18 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18923</v>
+        <v>18888</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국민연금공단</t>
+          <t>국민건강보험공단 일산병원</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -916,110 +916,104 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>19350</v>
+        <v>18923</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
+          <t>국민연금공단</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>32627</v>
+        <v>19350</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>국방과학연구소</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>28199</v>
+        <v>32627</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>아리랑TV미디어</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>32026</v>
+        <v>28199</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1035,208 +1029,208 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>지케이엘위드주식회사</t>
+          <t>아리랑TV미디어</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>29463</v>
+        <v>32026</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>극지연구소</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>지케이엘위드주식회사</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>27696</v>
+        <v>29463</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
+          <t>극지연구소</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>172596</v>
+        <v>27696</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>기술보증기금</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>35</v>
+      </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>18905</v>
+        <v>172596</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>주식회사 메디밸리파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>27790</v>
+        <v>18905</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>대구경북첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>주식회사 메디밸리파트너스</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30071</v>
+        <v>27790</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>32440</v>
+        <v>30071</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>독립기념관</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1245,30 +1239,30 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(주)한빛씨에스</t>
+          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>30983</v>
+        <v>32440</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1277,81 +1271,81 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
+          <t>(주)한빛씨에스</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>54782</v>
+        <v>30983</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>부산항만공사</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>18890</v>
+        <v>54782</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
+          <t>북한이탈주민지원재단</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>이지케어텍</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>35065</v>
+        <v>18890</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>분당서울대학교병원</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1367,90 +1361,90 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>티피에스주식회사</t>
+          <t>이지케어텍</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>30950</v>
+        <v>35065</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>티피에스주식회사</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>27730</v>
+        <v>30950</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>(주)국민행복기금</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>27691</v>
+        <v>27730</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1459,109 +1453,113 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
+          <t>(주)국민행복기금</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>37764</v>
+        <v>27691</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>서울대학교병원</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>18896</v>
+        <v>37764</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
+          <t>서울대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>50216</v>
+        <v>18896</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>서울올림픽기념국민체육진흥공단</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>38439</v>
+        <v>50216</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1578,141 +1576,137 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>29493</v>
+        <v>38439</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>수도권매립지관리공사</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>18887</v>
+        <v>29493</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>38</v>
-      </c>
+          <t>식품안전정보원</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>165900</v>
+        <v>18887</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>신용보증기금</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>38</v>
+      </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>18891</v>
+        <v>165900</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2</v>
-      </c>
+          <t>에너지경제연구원</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>32666</v>
+        <v>18891</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>연구개발특구진흥재단</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1721,30 +1715,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(주)연구개발특구에프엔에스</t>
+          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>45372</v>
+        <v>32666</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>연구개발특구진흥재단</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1753,30 +1747,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
+          <t>(주)연구개발특구에프엔에스</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>58855</v>
+        <v>45372</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1785,23 +1779,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>케이바이오스타트</t>
+          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>27693</v>
+        <v>58855</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1817,30 +1811,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>울산항만관리(주)</t>
+          <t>케이바이오스타트</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>35740</v>
+        <v>27693</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1849,30 +1843,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
+          <t>울산항만관리(주)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>52270</v>
+        <v>35740</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1881,49 +1875,55 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>인천항보안공사</t>
+          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>29461</v>
+        <v>52270</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>인천항만공사</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>인천항보안공사</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>18916</v>
+        <v>29461</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
+          <t>재단법인 대한건설기계안전관리원</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1938,164 +1938,158 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>18900</v>
+        <v>18916</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+          <t>전국재해구호협회</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>25444</v>
+        <v>18900</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>정보통신기획평가원</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>18886</v>
+        <v>25444</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3</v>
-      </c>
+          <t>정보통신정책연구원</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>43079</v>
+        <v>18886</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>주식회사 에스알</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>28132</v>
+        <v>43079</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>주식회사 에스알</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>220529</v>
+        <v>28132</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>중소기업은행</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2111,30 +2105,30 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>253988</v>
+        <v>220529</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
+          <t>중소기업은행</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2143,109 +2137,113 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
+          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>79797</v>
+        <v>253988</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>중소벤처기업진흥공단</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5</v>
+      </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>18892</v>
+        <v>79797</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
+          <t>충남대학교병원</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>(주)케이아이비보험중개</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>39613</v>
+        <v>18892</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코레일유통(주)</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>(주)케이아이비보험중개</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>59335</v>
+        <v>39613</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>코레일유통(주)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2262,57 +2260,53 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>29359</v>
+        <v>59335</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>태권도원운영관리(주)</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>27789</v>
+        <v>29359</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2321,116 +2315,116 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
+          <t>태권도원운영관리(주)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>125892</v>
+        <v>27789</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>한국개발연구원</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>27744</v>
+        <v>125892</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>한국개발연구원</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>18880</v>
+        <v>27744</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>4</v>
-      </c>
+          <t>한국고용정보원</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>44936</v>
+        <v>18880</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>한국공항공사</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2439,143 +2433,143 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
+          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>41895</v>
+        <v>44936</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국관세정보원</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>27699</v>
+        <v>41895</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>88687</v>
+        <v>27699</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>28118</v>
+        <v>88687</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>(주)코웍스</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>29463</v>
+        <v>28118</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2591,30 +2585,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>엘엑스파트너스(주)</t>
+          <t>(주)코웍스</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>33174</v>
+        <v>29463</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2623,30 +2617,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
+          <t>엘엑스파트너스(주)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>134226</v>
+        <v>33174</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2655,88 +2649,88 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
+          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>143254</v>
+        <v>134226</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>한국남부발전(주)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>9</v>
+      </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>18902</v>
+        <v>143254</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>2</v>
-      </c>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>에이플(주) | 칭다오aT물류유한공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>40884</v>
+        <v>18902</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
+          <t>한국농수산식품유통공사</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2745,30 +2739,30 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KRCThailand. Co.Ltd</t>
+          <t>에이플(주) | 칭다오aT물류유한공사</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>43161</v>
+        <v>40884</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국농어촌공사</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2777,30 +2771,30 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
+          <t>KRCThailand. Co.Ltd</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>59119</v>
+        <v>43161</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2809,30 +2803,30 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>도로교통안전관리주식회사</t>
+          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>35352</v>
+        <v>59119</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2841,30 +2835,30 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
+          <t>도로교통안전관리주식회사</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>120830</v>
+        <v>35352</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2873,81 +2867,81 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>베이징KIDP산업디자인서비스유한공사</t>
+          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>28660</v>
+        <v>120830</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>한국디자인진흥원</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>베이징KIDP산업디자인서비스유한공사</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>18898</v>
+        <v>28660</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국마사회</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>한국마사회시설관리(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>33120</v>
+        <v>18898</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국마사회</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2963,23 +2957,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>한국마사회시설관리(주)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>54973</v>
+        <v>33120</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2995,23 +2989,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>29388</v>
+        <v>54973</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3027,90 +3021,90 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>코바코파트너스주식회사</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29943</v>
+        <v>29388</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>코바코파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>40110</v>
+        <v>29943</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>44774</v>
+        <v>40110</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3119,90 +3113,90 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>코리아메디컬홀딩스</t>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>27747</v>
+        <v>44774</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>코리아메디컬홀딩스</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>28487</v>
+        <v>27747</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>알이비파트너스주식회사</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>37300</v>
+        <v>28487</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3211,266 +3205,266 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
+          <t>알이비파트너스주식회사</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>284521</v>
+        <v>37300</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>한국사학진흥재단</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>39</v>
+      </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>18897</v>
+        <v>284521</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>(주)포이파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>33084</v>
+        <v>18897</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산림복지진흥원</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>(주)포이파트너스</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>25486</v>
+        <v>33084</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>KTLChinaCo.,Ltd</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>29430</v>
+        <v>25486</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>KTLChinaCo.,Ltd</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>95626</v>
+        <v>29430</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>(주)키콕스파트너스</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>45150</v>
+        <v>95626</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>한국산업단지공단</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(주)키콕스파트너스</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>18916</v>
+        <v>45150</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>9</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>136049</v>
+        <v>18916</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>한국산업은행</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C103" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3479,148 +3473,148 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>110550</v>
+        <v>250563</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>58849</v>
+        <v>136049</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>한국석유공사</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>14</v>
+      </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>18896</v>
+        <v>110550</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국세라믹기술원</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>142356</v>
+        <v>58849</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>12</v>
-      </c>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>99981</v>
+        <v>18896</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3629,79 +3623,87 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>88925</v>
+        <v>142356</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국수자원공사</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>29355</v>
+        <v>99981</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>30080</v>
+        <v>88925</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3718,18 +3720,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>28175</v>
+        <v>29355</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3746,44 +3748,46 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>25674</v>
+        <v>30080</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>한국에너지기술평가원</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>18925</v>
+        <v>28175</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3800,168 +3804,158 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>27746</v>
+        <v>25674</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>28110</v>
+        <v>18925</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>한국원산지정보원</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>18896</v>
+        <v>27746</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>한국원자력안전기술원</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>31846</v>
+        <v>28110</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>29406</v>
+        <v>18896</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국원자력의학원</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>486796</v>
+        <v>31846</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3977,107 +3971,113 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>한국잡월드파트너즈(주)</t>
+          <t>KOFPI.PARAGUAY.S.A</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29539</v>
+        <v>29406</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>한국자산관리공사</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>70</v>
+      </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>18883</v>
+        <v>486796</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>한국잡월드</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한국잡월드파트너즈(주)</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>18891</v>
+        <v>29539</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>케이피엑스서비스원주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>28108</v>
+        <v>18883</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국전기안전공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>34716</v>
+        <v>18891</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국전력거래소</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4119,55 +4119,49 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>케이피엑스서비스원주식회사</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>45469</v>
+        <v>28108</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>3</v>
-      </c>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>36852</v>
+        <v>34716</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4183,30 +4177,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>한전기술서비스(주)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>30022</v>
+        <v>45469</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4215,30 +4209,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>179646</v>
+        <v>36852</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4247,30 +4241,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>40148</v>
+        <v>30022</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4279,56 +4273,62 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>47665</v>
+        <v>179646</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>18899</v>
+        <v>40148</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4337,176 +4337,176 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>105871</v>
+        <v>47665</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>30150</v>
+        <v>18899</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>27769</v>
+        <v>105871</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
+          <t>한국청소년활동진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>키와파트너스㈜</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157896</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>75106</v>
+        <v>30150</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>137010</v>
+        <v>27769</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>한국탄소산업진흥원</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>18</v>
+      </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157896</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>18884</v>
+        <v>75106</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4515,58 +4515,56 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IPKoreaCenterInc</t>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>29482</v>
+        <v>137010</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>47713</v>
+        <v>18884</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국특허기술진흥원</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4575,176 +4573,176 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+          <t>IPKoreaCenterInc</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>649841</v>
+        <v>29482</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
+          <t>한국해양과학기술원</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>67551</v>
+        <v>47713</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>74983</v>
+        <v>649841</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>한국해외인프라도시개발지원공사</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>KINDUSALLC</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>18900</v>
+        <v>67551</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>29949</v>
+        <v>74983</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한전KDN</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>25429</v>
+        <v>18900</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한국환경산업기술원</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4753,130 +4751,190 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+          <t>북경한능환보기술자문유한공사</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>40050</v>
+        <v>29949</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>32943</v>
+        <v>25429</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>한전KPS(주)</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>3</v>
+      </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>18897</v>
+        <v>40050</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>한전원자력연료주식회사</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>18898</v>
+        <v>32943</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>18897</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>18898</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
-      <c r="G150" t="n">
+      <c r="G152" t="n">
         <v>40376</v>
       </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3990,29 +3990,23 @@
           <t>한국자산관리공사</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>70</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486796</v>
+        <v>21160</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4292,29 +4286,23 @@
           <t>한국중소벤처기업유통원</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>2</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>40148</v>
+        <v>12336</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4620,29 +4608,23 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>93</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649841</v>
+        <v>25146</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3990,23 +3990,29 @@
           <t>한국자산관리공사</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>70</v>
+      </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>21160</v>
+        <v>486796</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4286,23 +4292,29 @@
           <t>한국중소벤처기업유통원</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>12336</v>
+        <v>40148</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4608,23 +4620,29 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>93</v>
+      </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>25146</v>
+        <v>649841</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -4475,24 +4475,24 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157896</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>75106</v>
+        <v>76708</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3460,29 +3460,23 @@
           <t>한국산업은행</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>48</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>250563</v>
+        <v>17523</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(주)강원랜드</t>
+          <t>(주)공영홈쇼핑</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -547,61 +547,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>(주)한국가스기술공사</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1024&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151757</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18889</v>
+        <v>31176</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+          <t>88관광개발(주)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>31176</v>
+        <v>18886</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
+          <t>가덕도신공항건설공단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -616,18 +616,18 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18886</v>
+        <v>18889</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>가덕도신공항건설공단</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -642,7 +642,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -653,33 +653,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>강원대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>18889</v>
+        <v>27742</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강원대학교치과병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -696,18 +698,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27742</v>
+        <v>28132</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>경북대학교병원</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -724,132 +726,130 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>28132</v>
+        <v>27748</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+          <t>경북대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27748</v>
+        <v>18885</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경북대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>공무원연금공단</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(주)상록골프앤리조트</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>18885</v>
+        <v>28717</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
+          <t>국가철도공단</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(주)상록골프앤리조트</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>28717</v>
+        <v>60742</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국가철도공단</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+          <t>국립농업박물관</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>60742</v>
+        <v>18890</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -864,18 +864,18 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>18890</v>
+        <v>18888</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국민건강보험공단 일산병원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -890,18 +890,18 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18888</v>
+        <v>18923</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국민건강보험공단 일산병원</t>
+          <t>국민연금공단</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -916,51 +916,57 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>18923</v>
+        <v>19350</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국민연금공단</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>국방과학연구소</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>19350</v>
+        <v>32627</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -969,90 +975,90 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
+          <t>아리랑TV미디어</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32627</v>
+        <v>32026</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>지케이엘위드주식회사</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>28199</v>
+        <v>29463</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>극지연구소</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>아리랑TV미디어</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>32026</v>
+        <v>27696</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1061,58 +1067,56 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>지케이엘위드주식회사</t>
+          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>29463</v>
+        <v>172596</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>극지연구소</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>27696</v>
+        <v>18905</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
+          <t>대구경북첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1121,56 +1125,58 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
+          <t>주식회사 메디밸리파트너스</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>172596</v>
+        <v>27790</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>18905</v>
+        <v>30071</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1179,58 +1185,62 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>주식회사 메디밸리파트너스</t>
+          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>27790</v>
+        <v>32440</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(주)한빛씨에스</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>30071</v>
+        <v>30983</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>부산항만공사</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1239,62 +1249,56 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>32440</v>
+        <v>54782</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>독립기념관</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
+          <t>북한이탈주민지원재단</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>(주)한빛씨에스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>30983</v>
+        <v>18890</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
+          <t>분당서울대학교병원</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1303,81 +1307,83 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
+          <t>이지케어텍</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>54782</v>
+        <v>35065</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>사립학교교직원연금공단</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>티피에스주식회사</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>18890</v>
+        <v>30950</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>이지케어텍</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>35065</v>
+        <v>27730</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1393,90 +1399,88 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>티피에스주식회사</t>
+          <t>(주)국민행복기금</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>30950</v>
+        <v>27691</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>27730</v>
+        <v>37764</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
+          <t>서울대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>(주)국민행복기금</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>27691</v>
+        <v>18896</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>서울올림픽기념국민체육진흥공단</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1485,137 +1489,137 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
+          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>37764</v>
+        <v>50216</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>선박해양플랜트연구소</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>18896</v>
+        <v>38439</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50216</v>
+        <v>29493</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+          <t>식품안전정보원</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>38439</v>
+        <v>18887</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
+          <t>신용보증기금</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>29493</v>
+        <v>165900</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
+          <t>에너지경제연구원</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1630,25 +1634,25 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>18887</v>
+        <v>18891</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1657,56 +1661,62 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
+          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>165900</v>
+        <v>32666</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>연구개발특구진흥재단</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(주)연구개발특구에프엔에스</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>18891</v>
+        <v>45372</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1715,23 +1725,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>32666</v>
+        <v>58855</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>연구개발특구진흥재단</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1747,30 +1757,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(주)연구개발특구에프엔에스</t>
+          <t>케이바이오스타트</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>45372</v>
+        <v>27693</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1779,30 +1789,30 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
+          <t>울산항만관리(주)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58855</v>
+        <v>35740</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1811,23 +1821,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>케이바이오스타트</t>
+          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>27693</v>
+        <v>52270</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>인천항만공사</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1843,113 +1853,103 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>울산항만관리(주)</t>
+          <t>인천항보안공사</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>35740</v>
+        <v>29461</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>7</v>
-      </c>
+          <t>재단법인 대한건설기계안전관리원</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>52270</v>
+        <v>18916</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
+          <t>전국재해구호협회</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>인천항보안공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>29461</v>
+        <v>18900</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>정보통신기획평가원</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>18916</v>
+        <v>25444</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
+          <t>정보통신정책연구원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1964,79 +1964,85 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>18900</v>
+        <v>18886</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>25444</v>
+        <v>43079</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>주식회사 에스알</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>18886</v>
+        <v>28132</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2045,58 +2051,62 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>43079</v>
+        <v>220529</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>주식회사 에스알</t>
+          <t>중소기업은행</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>28132</v>
+        <v>253988</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2105,62 +2115,56 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>220529</v>
+        <v>79797</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>중소기업은행</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>48</v>
-      </c>
+          <t>충남대학교병원</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>253988</v>
+        <v>18892</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2169,294 +2173,296 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
+          <t>(주)케이아이비보험중개</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>79797</v>
+        <v>39613</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>코레일유통(주)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>18892</v>
+        <v>59335</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(주)케이아이비보험중개</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>39613</v>
+        <v>29359</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코레일유통(주)</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>태권도원운영관리(주)</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>59335</v>
+        <v>27789</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>29359</v>
+        <v>125892</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>한국개발연구원</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>태권도원운영관리(주)</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>27789</v>
+        <v>27744</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>21</v>
-      </c>
+          <t>한국고용정보원</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>125892</v>
+        <v>18880</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>한국개발연구원</t>
+          <t>한국공항공사</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>27744</v>
+        <v>44936</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>한국관광공사</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>18880</v>
+        <v>41895</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>44936</v>
+        <v>27699</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2465,23 +2471,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
+          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>41895</v>
+        <v>88687</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국관세정보원</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2498,25 +2504,25 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>27699</v>
+        <v>28118</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2525,58 +2531,62 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
+          <t>(주)코웍스</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>88687</v>
+        <v>29463</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>엘엑스파트너스(주)</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>28118</v>
+        <v>33174</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2585,30 +2595,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(주)코웍스</t>
+          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>29463</v>
+        <v>134226</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2617,62 +2627,56 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>엘엑스파트너스(주)</t>
+          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>33174</v>
+        <v>143254</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>17</v>
-      </c>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>134226</v>
+        <v>18902</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
+          <t>한국농수산식품유통공사</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2681,56 +2685,62 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
+          <t>에이플(주) | 칭다오aT물류유한공사</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>143254</v>
+        <v>40884</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>한국농어촌공사</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>KRCThailand. Co.Ltd</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>18902</v>
+        <v>43161</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2739,23 +2749,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>에이플(주) | 칭다오aT물류유한공사</t>
+          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>40884</v>
+        <v>59119</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2771,30 +2781,30 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KRCThailand. Co.Ltd</t>
+          <t>도로교통안전관리주식회사</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>43161</v>
+        <v>35352</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2803,23 +2813,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
+          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>59119</v>
+        <v>120830</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국디자인진흥원</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2835,55 +2845,49 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>도로교통안전관리주식회사</t>
+          <t>베이징KIDP산업디자인서비스유한공사</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>35352</v>
+        <v>28660</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>9</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>120830</v>
+        <v>18898</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
+          <t>한국마사회</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2899,49 +2903,55 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>베이징KIDP산업디자인서비스유한공사</t>
+          <t>한국마사회시설관리(주)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>28660</v>
+        <v>33120</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>한국무역보험공사</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>주식회사 신아에스비(SLS조선)</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>18898</v>
+        <v>54973</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국마사회</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2957,23 +2967,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한국마사회시설관리(주)</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>33120</v>
+        <v>29388</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2989,62 +2999,58 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>코바코파트너스주식회사</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>54973</v>
+        <v>29943</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>한국문화진흥(주)</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29388</v>
+        <v>40110</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3053,83 +3059,83 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>코바코파트너스주식회사</t>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>29943</v>
+        <v>44774</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>코리아메디컬홀딩스</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>40110</v>
+        <v>27747</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>44774</v>
+        <v>28487</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3145,90 +3151,88 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>코리아메디컬홀딩스</t>
+          <t>알이비파트너스주식회사</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>27747</v>
+        <v>37300</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>28487</v>
+        <v>284521</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>알이비파트너스주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>37300</v>
+        <v>18897</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>한국산림복지진흥원</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3237,49 +3241,51 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
+          <t>(주)포이파트너스</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>284521</v>
+        <v>33084</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>한국산업기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>18897</v>
+        <v>25486</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3295,23 +3301,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(주)포이파트너스</t>
+          <t>KTLChinaCo.,Ltd</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>33084</v>
+        <v>29430</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3328,18 +3334,18 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>25486</v>
+        <v>95626</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3355,58 +3361,56 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KTLChinaCo.,Ltd</t>
+          <t>(주)키콕스파트너스</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>29430</v>
+        <v>45150</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>95626</v>
+        <v>18916</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국산업은행</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3415,200 +3419,212 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(주)키콕스파트너스</t>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>45150</v>
+        <v>250563</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>한국서부발전(주)</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>9</v>
+      </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>18916</v>
+        <v>136049</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>한국석유공사</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>14</v>
+      </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>17523</v>
+        <v>110550</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국세라믹기술원</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>136049</v>
+        <v>58849</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>14</v>
-      </c>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>110550</v>
+        <v>18896</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>58849</v>
+        <v>142356</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>한국수자원공사</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>12</v>
+      </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>18896</v>
+        <v>99981</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3617,87 +3633,79 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>142356</v>
+        <v>88925</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>99981</v>
+        <v>29355</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>88925</v>
+        <v>30080</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국에너지기술평가원</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3714,18 +3722,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>29355</v>
+        <v>28175</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3742,46 +3750,44 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30080</v>
+        <v>25674</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>28175</v>
+        <v>18925</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국원산지정보원</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3798,158 +3804,162 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>25674</v>
+        <v>27746</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>한국원자력안전기술원</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>18925</v>
+        <v>28110</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>27746</v>
+        <v>18896</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
+          <t>한국원자력의학원</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>28110</v>
+        <v>31846</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>KOFPI.PARAGUAY.S.A</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>18896</v>
+        <v>29406</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+          <t>한국자산관리공사</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>31846</v>
+        <v>21160</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3965,113 +3975,107 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
+          <t>한국잡월드파트너즈(주)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29406</v>
+        <v>29539</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>70</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486796</v>
+        <v>18883</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전기안전공사</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>한국잡월드파트너즈(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>29539</v>
+        <v>18891</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>케이피엑스서비스원주식회사</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>18883</v>
+        <v>28108</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국전력공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4086,18 +4090,18 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>18891</v>
+        <v>34716</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4113,49 +4117,55 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>케이피엑스서비스원주식회사</t>
+          <t>한전기술서비스(주)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>28108</v>
+        <v>45469</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>한국조폐공사</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>34716</v>
+        <v>36852</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4171,30 +4181,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>45469</v>
+        <v>30022</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4203,30 +4213,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>36852</v>
+        <v>179646</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4235,30 +4245,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>30022</v>
+        <v>40148</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4267,62 +4277,56 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>179646</v>
+        <v>47665</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>2</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>40148</v>
+        <v>18899</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4331,176 +4335,176 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>47665</v>
+        <v>105871</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>한국청소년활동진흥원</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>키와파트너스㈜</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>18899</v>
+        <v>30150</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>105871</v>
+        <v>27769</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국탄소산업진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>30150</v>
+        <v>76708</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>27769</v>
+        <v>137010</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>76708</v>
+        <v>18884</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>한국특허기술진흥원</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4509,234 +4513,230 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+          <t>IPKoreaCenterInc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>137010</v>
+        <v>29482</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>한국해양과학기술원</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18884</v>
+        <v>47713</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1</v>
-      </c>
+          <t>한국해양진흥공사</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>IPKoreaCenterInc</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>29482</v>
+        <v>25146</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>한국해외인프라도시개발지원공사</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KINDUSALLC</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>47713</v>
+        <v>67551</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649841</v>
+        <v>74983</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>67551</v>
+        <v>18900</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국환경산업기술원</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>74983</v>
+        <v>29949</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>한전KDN</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>18900</v>
+        <v>25429</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4745,190 +4745,130 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>북경한능환보기술자문유한공사</t>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>29949</v>
+        <v>40050</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한전원자력연료주식회사</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>25429</v>
+        <v>32943</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>3</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>40050</v>
+        <v>18897</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>2</v>
-      </c>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>32943</v>
+        <v>18898</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>18897</v>
+        <v>40376</v>
       </c>
       <c r="H150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
-        <v>18898</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>40376</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18901</v>
+        <v>18903</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>29916</v>
+        <v>29918</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
+          <t>(주)강원랜드</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -540,68 +540,68 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38633</v>
+        <v>38635</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+          <t>(주)공영홈쇼핑</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1024&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151757</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>31176</v>
+        <v>18891</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>(주)한국가스기술공사</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18886</v>
+        <v>31178</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가덕도신공항건설공단</t>
+          <t>88관광개발(주)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -616,18 +616,18 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18889</v>
+        <v>18888</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
+          <t>가덕도신공항건설공단</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -642,46 +642,44 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18889</v>
+        <v>18891</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강원대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+          <t>가축위생방역지원본부</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27742</v>
+        <v>18891</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>강원대학교치과병원</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -698,18 +696,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>28132</v>
+        <v>27744</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -726,130 +724,132 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>27748</v>
+        <v>28134</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>경북대학교병원</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>18885</v>
+        <v>27750</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+          <t>경북대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(주)상록골프앤리조트</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>28717</v>
+        <v>18887</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>국가철도공단</t>
+          <t>공무원연금공단</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(주)상록골프앤리조트</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>60742</v>
+        <v>28719</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>국가철도공단</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>18890</v>
+        <v>60744</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국립농업박물관</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -864,18 +864,18 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>18888</v>
+        <v>18892</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>국민건강보험공단 일산병원</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -890,18 +890,18 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18923</v>
+        <v>18890</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국민연금공단</t>
+          <t>국민건강보험공단 일산병원</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -916,57 +916,51 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>19350</v>
+        <v>18925</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
+          <t>국민연금공단</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>32627</v>
+        <v>19352</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>국방과학연구소</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -975,90 +969,90 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>아리랑TV미디어</t>
+          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32026</v>
+        <v>32629</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>지케이엘위드주식회사</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>29463</v>
+        <v>28201</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>극지연구소</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>아리랑TV미디어</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>27696</v>
+        <v>32028</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1067,56 +1061,58 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
+          <t>지케이엘위드주식회사</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>172596</v>
+        <v>29465</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>극지연구소</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18905</v>
+        <v>27698</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1125,58 +1121,56 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>주식회사 메디밸리파트너스</t>
+          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>27790</v>
+        <v>172598</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>30071</v>
+        <v>18907</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>대구경북첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1185,62 +1179,58 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+          <t>주식회사 메디밸리파트너스</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>32440</v>
+        <v>27792</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>독립기념관</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>(주)한빛씨에스</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>30983</v>
+        <v>30073</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1249,56 +1239,62 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
+          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>54782</v>
+        <v>32442</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>독립기념관</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(주)한빛씨에스</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>18890</v>
+        <v>30985</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
+          <t>부산항만공사</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1307,83 +1303,81 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>이지케어텍</t>
+          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>35065</v>
+        <v>54784</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
+          <t>북한이탈주민지원재단</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>티피에스주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>30950</v>
+        <v>18892</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>분당서울대학교병원</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>이지케어텍</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>27730</v>
+        <v>35067</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1399,88 +1393,90 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(주)국민행복기금</t>
+          <t>티피에스주식회사</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>27691</v>
+        <v>30952</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>37764</v>
+        <v>27732</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>서민금융진흥원</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>(주)국민행복기금</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>18896</v>
+        <v>27693</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1489,137 +1485,137 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
+          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>50216</v>
+        <v>37766</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+          <t>서울대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>38439</v>
+        <v>18898</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
+          <t>서울올림픽기념국민체육진흥공단</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>29493</v>
+        <v>50218</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>선박해양플랜트연구소</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>18887</v>
+        <v>38441</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>165900</v>
+        <v>29495</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
+          <t>식품안전정보원</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1634,25 +1630,25 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>18891</v>
+        <v>18889</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>신용보증기금</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1661,62 +1657,56 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>32666</v>
+        <v>165902</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>연구개발특구진흥재단</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
+          <t>에너지경제연구원</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>(주)연구개발특구에프엔에스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>45372</v>
+        <v>18893</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1725,23 +1715,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
+          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>58855</v>
+        <v>32668</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>연구개발특구진흥재단</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1757,30 +1747,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>케이바이오스타트</t>
+          <t>(주)연구개발특구에프엔에스</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>27693</v>
+        <v>45374</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1789,30 +1779,30 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>울산항만관리(주)</t>
+          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>35740</v>
+        <v>58857</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1821,23 +1811,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
+          <t>케이바이오스타트</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>52270</v>
+        <v>27695</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1853,103 +1843,113 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>인천항보안공사</t>
+          <t>울산항만관리(주)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>29461</v>
+        <v>35742</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>인천국제공항공사</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>7</v>
+      </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>18916</v>
+        <v>52272</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>인천항만공사</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>인천항보안공사</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>18900</v>
+        <v>29463</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
+          <t>재단법인 대한건설기계안전관리원</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>25444</v>
+        <v>18918</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1964,85 +1964,79 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>18886</v>
+        <v>18902</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>정보통신기획평가원</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>43079</v>
+        <v>25446</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>주식회사 에스알</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+          <t>정보통신정책연구원</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>28132</v>
+        <v>18888</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2051,62 +2045,58 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>220529</v>
+        <v>43081</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>중소기업은행</t>
+          <t>주식회사 에스알</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>253988</v>
+        <v>28134</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2115,56 +2105,62 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>79797</v>
+        <v>220531</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>중소기업은행</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>48</v>
+      </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>18892</v>
+        <v>253990</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2173,296 +2169,294 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(주)케이아이비보험중개</t>
+          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>39613</v>
+        <v>79799</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>코레일유통(주)</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+          <t>충남대학교병원</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>59335</v>
+        <v>18894</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>(주)케이아이비보험중개</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>29359</v>
+        <v>39615</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>코레일유통(주)</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>태권도원운영관리(주)</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>27789</v>
+        <v>59337</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>125892</v>
+        <v>29361</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>한국개발연구원</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>태권도원운영관리(주)</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>27744</v>
+        <v>27791</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>한국가스공사</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>21</v>
+      </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>18880</v>
+        <v>125894</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
+          <t>한국개발연구원</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>44936</v>
+        <v>27746</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>2</v>
-      </c>
+          <t>한국고용정보원</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>41895</v>
+        <v>18882</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국관세정보원</t>
+          <t>한국공항공사</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>27699</v>
+        <v>44938</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2471,23 +2465,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
+          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>88687</v>
+        <v>41897</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2504,25 +2498,25 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>28118</v>
+        <v>27701</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2531,62 +2525,58 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(주)코웍스</t>
+          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>29463</v>
+        <v>88689</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>엘엑스파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>33174</v>
+        <v>28120</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2595,30 +2585,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
+          <t>(주)코웍스</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>134226</v>
+        <v>29465</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2627,56 +2617,62 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
+          <t>엘엑스파트너스(주)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>143254</v>
+        <v>33176</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>한국남동발전(주)</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>17</v>
+      </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>18902</v>
+        <v>134228</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2685,62 +2681,56 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>에이플(주) | 칭다오aT물류유한공사</t>
+          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>40884</v>
+        <v>143256</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>KRCThailand. Co.Ltd</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>43161</v>
+        <v>18904</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국농수산식품유통공사</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2749,23 +2739,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
+          <t>에이플(주) | 칭다오aT물류유한공사</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>59119</v>
+        <v>40886</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국농어촌공사</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2781,30 +2771,30 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>도로교통안전관리주식회사</t>
+          <t>KRCThailand. Co.Ltd</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>35352</v>
+        <v>43163</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2813,23 +2803,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
+          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>120830</v>
+        <v>59121</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2845,49 +2835,55 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>베이징KIDP산업디자인서비스유한공사</t>
+          <t>도로교통안전관리주식회사</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>28660</v>
+        <v>35354</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>한국동서발전(주)</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>9</v>
+      </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>18898</v>
+        <v>120832</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국마사회</t>
+          <t>한국디자인진흥원</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2903,55 +2899,49 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>한국마사회시설관리(주)</t>
+          <t>베이징KIDP산업디자인서비스유한공사</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>33120</v>
+        <v>28662</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>54973</v>
+        <v>18900</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국마사회</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2967,23 +2957,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>한국마사회시설관리(주)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>29388</v>
+        <v>33122</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2999,58 +2989,62 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>코바코파트너스주식회사</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>29943</v>
+        <v>54975</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한국문화진흥(주)</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>40110</v>
+        <v>29390</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3059,83 +3053,83 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+          <t>코바코파트너스주식회사</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>44774</v>
+        <v>29945</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>코리아메디컬홀딩스</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>27747</v>
+        <v>40112</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>28487</v>
+        <v>44776</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3151,88 +3145,90 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>알이비파트너스주식회사</t>
+          <t>코리아메디컬홀딩스</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>37300</v>
+        <v>27749</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>284521</v>
+        <v>28489</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>한국부동산원</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>알이비파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>18897</v>
+        <v>37302</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3241,51 +3237,49 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(주)포이파트너스</t>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>33084</v>
+        <v>284523</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>25486</v>
+        <v>18899</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산림복지진흥원</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3301,23 +3295,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KTLChinaCo.,Ltd</t>
+          <t>(주)포이파트너스</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>29430</v>
+        <v>33086</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3334,18 +3328,18 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>95626</v>
+        <v>25488</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3361,56 +3355,58 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(주)키콕스파트너스</t>
+          <t>KTLChinaCo.,Ltd</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>45150</v>
+        <v>29432</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>한국산업기술진흥원</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>18916</v>
+        <v>95628</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3419,62 +3415,56 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+          <t>(주)키콕스파트너스</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>250563</v>
+        <v>45152</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>9</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>136049</v>
+        <v>18918</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>한국산업은행</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C103" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3483,148 +3473,148 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>110550</v>
+        <v>250565</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>58849</v>
+        <v>136051</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>한국석유공사</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>14</v>
+      </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>18896</v>
+        <v>110552</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국세라믹기술원</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>142356</v>
+        <v>58851</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>12</v>
-      </c>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>99981</v>
+        <v>18898</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3633,79 +3623,87 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>88925</v>
+        <v>142358</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국수자원공사</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>29355</v>
+        <v>99983</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>30080</v>
+        <v>88927</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3722,18 +3720,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>28175</v>
+        <v>29357</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3750,44 +3748,46 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>25674</v>
+        <v>30082</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>한국에너지기술평가원</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>18925</v>
+        <v>28177</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3804,162 +3804,158 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>27746</v>
+        <v>25676</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>28110</v>
+        <v>18927</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>한국원산지정보원</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>18896</v>
+        <v>27748</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>한국원자력안전기술원</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>31846</v>
+        <v>28112</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>29406</v>
+        <v>18898</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>한국원자력의학원</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>21160</v>
+        <v>31848</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3975,107 +3971,113 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>한국잡월드파트너즈(주)</t>
+          <t>KOFPI.PARAGUAY.S.A</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29539</v>
+        <v>29408</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>한국자산관리공사</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>70</v>
+      </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>18883</v>
+        <v>486798</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>한국잡월드</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한국잡월드파트너즈(주)</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>18891</v>
+        <v>29541</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>케이피엑스서비스원주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>28108</v>
+        <v>18885</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국전기안전공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4090,18 +4092,18 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>34716</v>
+        <v>18893</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국전력거래소</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4117,55 +4119,49 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>케이피엑스서비스원주식회사</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>45469</v>
+        <v>28110</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>3</v>
-      </c>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>36852</v>
+        <v>34718</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4181,30 +4177,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>한전기술서비스(주)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>30022</v>
+        <v>45471</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4213,30 +4209,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>179646</v>
+        <v>36854</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4245,30 +4241,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>40148</v>
+        <v>30024</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4277,56 +4273,62 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>47665</v>
+        <v>179648</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>18899</v>
+        <v>40150</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4335,176 +4337,176 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>105871</v>
+        <v>47667</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>30150</v>
+        <v>18901</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>27769</v>
+        <v>105873</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
+          <t>한국청소년활동진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>키와파트너스㈜</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>76708</v>
+        <v>30152</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>137010</v>
+        <v>27771</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>한국탄소산업진흥원</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>18884</v>
+        <v>76710</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4513,230 +4515,234 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IPKoreaCenterInc</t>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>29482</v>
+        <v>137012</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>47713</v>
+        <v>18886</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>한국특허기술진흥원</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>IPKoreaCenterInc</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>25146</v>
+        <v>29484</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
+          <t>한국해양과학기술원</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>67551</v>
+        <v>47715</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>74983</v>
+        <v>649843</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>한국해외인프라도시개발지원공사</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>KINDUSALLC</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>18900</v>
+        <v>67553</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>29949</v>
+        <v>74985</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한전KDN</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>25429</v>
+        <v>18902</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한국환경산업기술원</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4745,130 +4751,190 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+          <t>북경한능환보기술자문유한공사</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>40050</v>
+        <v>29951</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>32943</v>
+        <v>25431</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>한전KPS(주)</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>3</v>
+      </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>18897</v>
+        <v>40052</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>한전원자력연료주식회사</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>18898</v>
+        <v>32945</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>18899</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>18900</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>40376</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="G152" t="n">
+        <v>40378</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3460,29 +3460,23 @@
           <t>한국산업은행</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>48</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>250565</v>
+        <v>17525</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -4620,29 +4614,23 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>93</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649843</v>
+        <v>25148</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3460,23 +3460,29 @@
           <t>한국산업은행</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>48</v>
+      </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>17525</v>
+        <v>250565</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -4614,23 +4620,29 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>93</v>
+      </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>25148</v>
+        <v>649843</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3460,29 +3460,23 @@
           <t>한국산업은행</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>48</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>250565</v>
+        <v>17525</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3660,11 +3654,11 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026041703163320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>99983</v>
+        <v>107466</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3990,29 +3984,23 @@
           <t>한국자산관리공사</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>70</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486798</v>
+        <v>21162</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4620,29 +4608,23 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>93</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649843</v>
+        <v>25148</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -3460,23 +3460,29 @@
           <t>한국산업은행</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>48</v>
+      </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>17525</v>
+        <v>250565</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3984,23 +3990,29 @@
           <t>한국자산관리공사</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>70</v>
+      </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>21162</v>
+        <v>486798</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4608,23 +4620,29 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>93</v>
+      </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>25148</v>
+        <v>649843</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,7 +2883,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
+          <t>한국로봇산업진흥원</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2915,33 +2915,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>한국마사회</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한국마사회시설관리(주)</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>18900</v>
+        <v>33122</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국마사회</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2957,23 +2963,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한국마사회시설관리(주)</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>33122</v>
+        <v>54975</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2989,23 +2995,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>54975</v>
+        <v>29390</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3021,90 +3027,90 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>코바코파트너스주식회사</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29390</v>
+        <v>29945</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>코바코파트너스주식회사</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>29945</v>
+        <v>40112</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>40112</v>
+        <v>44776</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3113,90 +3119,90 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+          <t>코리아메디컬홀딩스</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>44776</v>
+        <v>27749</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>코리아메디컬홀딩스</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>27749</v>
+        <v>28489</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>알이비파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>28489</v>
+        <v>37302</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3205,266 +3211,266 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>알이비파트너스주식회사</t>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>37302</v>
+        <v>284523</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>39</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>284523</v>
+        <v>18899</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>한국산림복지진흥원</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(주)포이파트너스</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>18899</v>
+        <v>33086</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>(주)포이파트너스</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>33086</v>
+        <v>25488</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>KTLChinaCo.,Ltd</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>25488</v>
+        <v>29432</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>KTLChinaCo.,Ltd</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>29432</v>
+        <v>95628</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(주)키콕스파트너스</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>95628</v>
+        <v>45152</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>(주)키콕스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>45152</v>
+        <v>18918</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>한국산업은행</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>48</v>
+      </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>18918</v>
+        <v>250565</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C103" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3473,30 +3479,30 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>250565</v>
+        <v>136051</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국석유공사</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3505,116 +3511,116 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>136051</v>
+        <v>110552</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>한국세라믹기술원</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>110552</v>
+        <v>58851</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>58851</v>
+        <v>18898</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>한국수력원자력(주)</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>11</v>
+      </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>18898</v>
+        <v>142358</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국수자원공사</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3623,30 +3629,30 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>142358</v>
+        <v>107466</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3655,55 +3661,51 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>107466</v>
+        <v>88927</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>88927</v>
+        <v>29357</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3720,18 +3722,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>29357</v>
+        <v>30082</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국에너지기술평가원</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3748,18 +3750,18 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30082</v>
+        <v>28177</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3776,193 +3778,197 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>28177</v>
+        <v>25676</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>25676</v>
+        <v>18927</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>한국원산지정보원</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>18927</v>
+        <v>27748</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
+          <t>한국원자력안전기술원</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>27748</v>
+        <v>28112</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>28112</v>
+        <v>18898</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>한국원자력의학원</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>18898</v>
+        <v>31848</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>KOFPI.PARAGUAY.S.A</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>31848</v>
+        <v>29408</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3971,30 +3977,30 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29408</v>
+        <v>486798</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4003,55 +4009,49 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+          <t>한국잡월드파트너즈(주)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486798</v>
+        <v>29541</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>한국잡월드파트너즈(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>29541</v>
+        <v>18885</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
+          <t>한국전기안전공사</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4066,109 +4066,115 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>18885</v>
+        <v>18893</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>케이피엑스서비스원주식회사</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>18893</v>
+        <v>28110</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>케이피엑스서비스원주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>28110</v>
+        <v>34718</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>한국전력기술주식회사</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>한전기술서비스(주)</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>34718</v>
+        <v>45471</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4177,30 +4183,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>45471</v>
+        <v>36854</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4209,30 +4215,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>36854</v>
+        <v>30024</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4241,30 +4247,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>30024</v>
+        <v>179648</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4273,30 +4279,30 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>179648</v>
+        <v>40150</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4305,88 +4311,88 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>40150</v>
+        <v>47667</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>3</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>47667</v>
+        <v>18901</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>한국철도공사</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>5</v>
+      </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>18901</v>
+        <v>105873</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국청소년활동진흥원</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4395,55 +4401,51 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+          <t>키와파트너스㈜</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>105873</v>
+        <v>30152</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>30152</v>
+        <v>27771</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국탄소산업진흥원</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -4460,171 +4462,175 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>27771</v>
+        <v>76710</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>76710</v>
+        <v>137012</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>5</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>137012</v>
+        <v>18886</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>한국특허기술진흥원</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>IPKoreaCenterInc</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18886</v>
+        <v>29484</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
+          <t>한국해양과학기술원</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>IPKoreaCenterInc</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>29484</v>
+        <v>47715</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>47715</v>
+        <v>649843</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국해외인프라도시개발지원공사</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -4633,176 +4639,176 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+          <t>KINDUSALLC</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649843</v>
+        <v>67553</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>67553</v>
+        <v>74985</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>74985</v>
+        <v>18902</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>18902</v>
+        <v>29951</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>29951</v>
+        <v>25431</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>25431</v>
+        <v>40052</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한전원자력연료주식회사</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4811,55 +4817,49 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>40052</v>
+        <v>32945</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>2</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>32945</v>
+        <v>18899</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
+          <t>해양수산과학기술진흥원</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4874,67 +4874,41 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>18899</v>
+        <v>18900</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>18900</v>
+        <v>40378</v>
       </c>
       <c r="H151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>40378</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2092,29 +2092,23 @@
           <t>주택도시보증공사</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>48</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>220531</v>
+        <v>16197</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2883,7 +2877,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
+          <t>한국디자인진흥원</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2915,39 +2909,33 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국마사회</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>한국마사회시설관리(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>33122</v>
+        <v>18900</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국마사회</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2963,23 +2951,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>한국마사회시설관리(주)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>54975</v>
+        <v>33122</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2995,23 +2983,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>29390</v>
+        <v>54975</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3027,90 +3015,90 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>코바코파트너스주식회사</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29945</v>
+        <v>29390</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>코바코파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>40112</v>
+        <v>29945</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>44776</v>
+        <v>40112</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3119,90 +3107,90 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>코리아메디컬홀딩스</t>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>27749</v>
+        <v>44776</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>코리아메디컬홀딩스</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>28489</v>
+        <v>27749</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>알이비파트너스주식회사</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>37302</v>
+        <v>28489</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3211,266 +3199,266 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
+          <t>알이비파트너스주식회사</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>284523</v>
+        <v>37302</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>한국사학진흥재단</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>39</v>
+      </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>18899</v>
+        <v>284523</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>(주)포이파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>33086</v>
+        <v>18899</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산림복지진흥원</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>(주)포이파트너스</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>25488</v>
+        <v>33086</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>KTLChinaCo.,Ltd</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>29432</v>
+        <v>25488</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>KTLChinaCo.,Ltd</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>95628</v>
+        <v>29432</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>(주)키콕스파트너스</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>45152</v>
+        <v>95628</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>한국산업단지공단</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(주)키콕스파트너스</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>18918</v>
+        <v>45152</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>48</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>250565</v>
+        <v>18918</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국산업은행</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3479,30 +3467,30 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>136051</v>
+        <v>250565</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C104" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3511,116 +3499,116 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>110552</v>
+        <v>136051</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국석유공사</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>58851</v>
+        <v>110552</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>한국세라믹기술원</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>18898</v>
+        <v>58851</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>11</v>
-      </c>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>142358</v>
+        <v>18898</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3629,30 +3617,30 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>107466</v>
+        <v>142358</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국수자원공사</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3661,51 +3649,55 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>88927</v>
+        <v>107466</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>29357</v>
+        <v>88927</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3722,18 +3714,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>30082</v>
+        <v>29357</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3750,18 +3742,18 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>28177</v>
+        <v>30082</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국에너지기술평가원</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3778,197 +3770,193 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>25676</v>
+        <v>28177</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>한국연구재단</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>18927</v>
+        <v>25676</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>27748</v>
+        <v>18927</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
+          <t>한국원산지정보원</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>28112</v>
+        <v>27748</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>한국원자력안전기술원</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>18898</v>
+        <v>28112</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>31848</v>
+        <v>18898</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국원자력의학원</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>29408</v>
+        <v>31848</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3977,30 +3965,30 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+          <t>KOFPI.PARAGUAY.S.A</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>486798</v>
+        <v>29408</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4009,49 +3997,55 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>한국잡월드파트너즈(주)</t>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>29541</v>
+        <v>486798</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>한국잡월드</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한국잡월드파트너즈(주)</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>18885</v>
+        <v>29541</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국장애인개발원</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4066,115 +4060,109 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>18893</v>
+        <v>18885</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전기안전공사</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>케이피엑스서비스원주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>28110</v>
+        <v>18893</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>케이피엑스서비스원주식회사</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>34718</v>
+        <v>28110</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>한전기술서비스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>45471</v>
+        <v>34718</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4183,30 +4171,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+          <t>한전기술서비스(주)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>36854</v>
+        <v>45471</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4215,30 +4203,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>30024</v>
+        <v>36854</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4247,30 +4235,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>179648</v>
+        <v>30024</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4279,30 +4267,30 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>40150</v>
+        <v>179648</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4311,88 +4299,88 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>47667</v>
+        <v>40150</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>한국지역난방공사</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3</v>
+      </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>18901</v>
+        <v>47667</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>5</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>105873</v>
+        <v>18901</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4401,51 +4389,55 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>키와파트너스㈜</t>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>30152</v>
+        <v>105873</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국청소년활동진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>키와파트너스㈜</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>27771</v>
+        <v>30152</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -4462,353 +4454,343 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>76710</v>
+        <v>27771</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>한국탄소산업진흥원</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>137012</v>
+        <v>76710</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>한국토지주택공사</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>5</v>
+      </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>18886</v>
+        <v>137012</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>IPKoreaCenterInc</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>29484</v>
+        <v>18886</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>한국특허기술진흥원</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>IPKoreaCenterInc</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>47715</v>
+        <v>29484</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국해양과학기술원</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>649843</v>
+        <v>47715</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1</v>
-      </c>
+          <t>한국해양진흥공사</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>67553</v>
+        <v>25148</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국해외인프라도시개발지원공사</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>KINDUSALLC</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>74985</v>
+        <v>67553</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>한국환경공단</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>18902</v>
+        <v>74985</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>29951</v>
+        <v>18902</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한국환경산업기술원</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>25431</v>
+        <v>29951</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>40052</v>
+        <v>25431</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4817,49 +4799,55 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>32945</v>
+        <v>40052</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>한전원자력연료주식회사</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>18899</v>
+        <v>32945</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
+          <t>항공안전기술원</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4874,41 +4862,67 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>18900</v>
+        <v>18899</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>18900</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
-      <c r="G151" t="n">
+      <c r="G152" t="n">
         <v>40378</v>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -2092,23 +2092,29 @@
           <t>주택도시보증공사</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>48</v>
+      </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>16197</v>
+        <v>220531</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -4614,23 +4620,29 @@
           <t>한국해양진흥공사</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>93</v>
+      </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>25148</v>
+        <v>649843</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4681,7 +4681,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국환경보전원</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4709,100 +4709,106 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>18902</v>
+        <v>29951</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>29951</v>
+        <v>25431</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>25431</v>
+        <v>40052</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한전원자력연료주식회사</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4811,55 +4817,49 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>40052</v>
+        <v>32945</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>2</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>32945</v>
+        <v>18899</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
+          <t>해양수산과학기술진흥원</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4874,67 +4874,41 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>18899</v>
+        <v>18900</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>18900</v>
+        <v>40378</v>
       </c>
       <c r="H151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>40378</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,121 +487,119 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(재)한국우편사업진흥원</t>
+          <t>(주)강원랜드</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(주)하이원추추파크 | (주)하이원파트너스</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0354&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154458</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0005&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157855</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>29918</v>
+        <v>38635</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(주)강원랜드</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
+          <t>(주)공영홈쇼핑</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(주)하이원추추파크 | (주)하이원파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0005&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157855</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1024&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151757</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38635</v>
+        <v>18891</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>(주)한국가스기술공사</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1024&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151757</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18891</v>
+        <v>31178</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+          <t>88관광개발(주)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0125&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155056</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>31178</v>
+        <v>18888</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
+          <t>가덕도신공항건설공단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -616,18 +614,18 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0001&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155677</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18888</v>
+        <v>18891</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>가덕도신공항건설공단</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -642,7 +640,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1399&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -653,33 +651,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>강원대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0002&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154645</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>18891</v>
+        <v>27744</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강원대학교치과병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -696,18 +696,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0003&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157213</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27744</v>
+        <v>28134</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>경북대학교병원</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -724,132 +724,130 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0006&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155275</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>28134</v>
+        <v>27750</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+          <t>경북대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0008&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159274</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27750</v>
+        <v>18887</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경북대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>공무원연금공단</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(주)상록골프앤리조트</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159566</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>18887</v>
+        <v>28719</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
+          <t>국가철도공단</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(주)상록골프앤리조트</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0013&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152640</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>28719</v>
+        <v>60744</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국가철도공단</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+          <t>국립농업박물관</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0270&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>60744</v>
+        <v>18892</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -864,18 +862,18 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1375&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154785</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>18892</v>
+        <v>18890</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국민건강보험공단 일산병원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -890,18 +888,18 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1324&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18890</v>
+        <v>18925</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국민건강보험공단 일산병원</t>
+          <t>국민연금공단</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -916,104 +914,110 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0459&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153049</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>18925</v>
+        <v>19352</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국민연금공단</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>국방과학연구소</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0028&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157409</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>19352</v>
+        <v>32629</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>주식회사 에이디디시설관리단 | 주식회사 에이디디보안환경관리단</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0345&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154538</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32629</v>
+        <v>28201</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>아리랑TV미디어</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>28201</v>
+        <v>32028</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1029,208 +1033,208 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>아리랑TV미디어</t>
+          <t>지케이엘위드주식회사</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>32028</v>
+        <v>29465</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>극지연구소</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>지케이엘위드주식회사</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>29465</v>
+        <v>27698</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>극지연구소</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>27698</v>
+        <v>172598</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>35</v>
-      </c>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>172598</v>
+        <v>18907</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>대구경북첨단의료산업진흥재단</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>주식회사 메디밸리파트너스</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>18907</v>
+        <v>27792</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>주식회사 메디밸리파트너스</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>27792</v>
+        <v>30073</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>30073</v>
+        <v>32442</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1239,30 +1243,30 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+          <t>(주)한빛씨에스</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>32442</v>
+        <v>30985</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>독립기념관</t>
+          <t>부산항만공사</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1271,81 +1275,81 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(주)한빛씨에스</t>
+          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>30985</v>
+        <v>54784</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3</v>
-      </c>
+          <t>북한이탈주민지원재단</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>54784</v>
+        <v>18892</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>분당서울대학교병원</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>이지케어텍</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>18892</v>
+        <v>35067</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1361,90 +1365,90 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>이지케어텍</t>
+          <t>티피에스주식회사</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>35067</v>
+        <v>30952</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>티피에스주식회사</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>30952</v>
+        <v>27732</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>(주)국민행복기금</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>27732</v>
+        <v>27693</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1453,113 +1457,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(주)국민행복기금</t>
+          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>27693</v>
+        <v>37766</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2</v>
-      </c>
+          <t>서울대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>37766</v>
+        <v>18898</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>서울올림픽기념국민체육진흥공단</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>18898</v>
+        <v>50218</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50218</v>
+        <v>38441</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1576,137 +1576,141 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>38441</v>
+        <v>29495</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+          <t>식품안전정보원</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>29495</v>
+        <v>18889</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>신용보증기금</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>38</v>
+      </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>18889</v>
+        <v>165902</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>38</v>
-      </c>
+          <t>에너지경제연구원</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>165902</v>
+        <v>18893</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>여수광양항만공사</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>18893</v>
+        <v>32668</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>연구개발특구진흥재단</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1715,30 +1719,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+          <t>(주)연구개발특구에프엔에스</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>32668</v>
+        <v>45374</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>연구개발특구진흥재단</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1747,30 +1751,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(주)연구개발특구에프엔에스</t>
+          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>45374</v>
+        <v>58857</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1779,23 +1783,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
+          <t>케이바이오스타트</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58857</v>
+        <v>27695</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1811,30 +1815,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>케이바이오스타트</t>
+          <t>울산항만관리(주)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>27695</v>
+        <v>35742</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1843,30 +1847,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>울산항만관리(주)</t>
+          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>35742</v>
+        <v>52272</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>인천항만공사</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1875,55 +1879,49 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
+          <t>인천항보안공사</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>52272</v>
+        <v>29463</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
+          <t>재단법인 대한건설기계안전관리원</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>인천항보안공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>29463</v>
+        <v>18918</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1938,158 +1936,164 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>18918</v>
+        <v>18902</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>정보통신기획평가원</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>18902</v>
+        <v>25446</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+          <t>정보통신정책연구원</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>25446</v>
+        <v>18888</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>제주국제자유도시개발센터</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>18888</v>
+        <v>43081</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>주식회사 에스알</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>43081</v>
+        <v>28134</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>주식회사 에스알</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>28134</v>
+        <v>220531</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>중소기업은행</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2105,30 +2109,30 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>220531</v>
+        <v>253990</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>중소기업은행</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2137,113 +2141,109 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
+          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>253990</v>
+        <v>79799</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>5</v>
-      </c>
+          <t>충남대학교병원</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>79799</v>
+        <v>18894</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>코레일네트웍스(주)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>(주)케이아이비보험중개</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>18894</v>
+        <v>39615</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>코레일유통(주)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(주)케이아이비보험중개</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>39615</v>
+        <v>59337</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코레일유통(주)</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2260,53 +2260,57 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>59337</v>
+        <v>29361</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>태권도원운영관리(주)</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>29361</v>
+        <v>27791</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2315,116 +2319,116 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>태권도원운영관리(주)</t>
+          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>27791</v>
+        <v>125894</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>한국개발연구원</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>125894</v>
+        <v>27746</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>한국개발연구원</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+          <t>한국고용정보원</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>27746</v>
+        <v>18882</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>한국공항공사</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>18882</v>
+        <v>44938</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2433,143 +2437,143 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>44938</v>
+        <v>41897</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>41897</v>
+        <v>27701</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국관세정보원</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>27701</v>
+        <v>88689</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>88689</v>
+        <v>28120</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>(주)코웍스</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>28120</v>
+        <v>29465</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2585,30 +2589,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(주)코웍스</t>
+          <t>엘엑스파트너스(주)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>29465</v>
+        <v>33176</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2617,30 +2621,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>엘엑스파트너스(주)</t>
+          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>33176</v>
+        <v>134228</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2649,88 +2653,88 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
+          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>134228</v>
+        <v>143256</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>9</v>
-      </c>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>143256</v>
+        <v>18904</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>한국농수산식품유통공사</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>에이플(주) | 칭다오aT물류유한공사</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>18904</v>
+        <v>40886</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국농어촌공사</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2739,30 +2743,30 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>에이플(주) | 칭다오aT물류유한공사</t>
+          <t>KRCThailand. Co.Ltd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>40886</v>
+        <v>43163</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2771,30 +2775,30 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KRCThailand. Co.Ltd</t>
+          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>43163</v>
+        <v>59121</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2803,30 +2807,30 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
+          <t>도로교통안전관리주식회사</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>59121</v>
+        <v>35354</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2835,30 +2839,30 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>도로교통안전관리주식회사</t>
+          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>35354</v>
+        <v>120832</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국디자인진흥원</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2867,81 +2871,81 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
+          <t>베이징KIDP산업디자인서비스유한공사</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>120832</v>
+        <v>28662</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>베이징KIDP산업디자인서비스유한공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>28662</v>
+        <v>18900</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>한국마사회</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한국마사회시설관리(주)</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>18900</v>
+        <v>33122</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국마사회</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2957,23 +2961,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한국마사회시설관리(주)</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>33122</v>
+        <v>54975</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2989,23 +2993,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>54975</v>
+        <v>29390</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3021,90 +3025,90 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>코바코파트너스주식회사</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29390</v>
+        <v>29945</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>코바코파트너스주식회사</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>29945</v>
+        <v>40112</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>40112</v>
+        <v>44776</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3113,90 +3117,90 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+          <t>코리아메디컬홀딩스</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>44776</v>
+        <v>27749</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>코리아메디컬홀딩스</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>27749</v>
+        <v>28489</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>알이비파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>28489</v>
+        <v>37302</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3205,266 +3209,266 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>알이비파트너스주식회사</t>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>37302</v>
+        <v>284523</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>39</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>284523</v>
+        <v>18899</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>한국산림복지진흥원</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(주)포이파트너스</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>18899</v>
+        <v>33086</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>(주)포이파트너스</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>33086</v>
+        <v>25488</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>KTLChinaCo.,Ltd</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>25488</v>
+        <v>29432</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>KTLChinaCo.,Ltd</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>29432</v>
+        <v>95628</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(주)키콕스파트너스</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>95628</v>
+        <v>45152</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>(주)키콕스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>45152</v>
+        <v>18918</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>한국산업은행</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>48</v>
+      </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>18918</v>
+        <v>250565</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C103" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3473,30 +3477,30 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>250565</v>
+        <v>136051</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국석유공사</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3505,116 +3509,122 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>136051</v>
+        <v>110552</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>한국소방산업기술원</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>110552</v>
+        <v>58851</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>58851</v>
+        <v>142358</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>한국수자원공사</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>12</v>
+      </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>18898</v>
+        <v>107466</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3623,87 +3633,79 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>경기그린에너지㈜ | 인천연료전지㈜ | 퍼스트키퍼스㈜ | 시큐텍㈜ | 에너지혁신성장펀드1호 | 디지털혁신성장펀드 | 원전산업성장펀드 | KHNPCanadaEnergyLtd. | KHNPUSALLC | KHNPChileSpA | LSGHydroPowerLtd.</t>
+          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0220&amp;reportFormRootNo=31901&amp;disclosureNo=2026071503216007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>142358</v>
+        <v>88927</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>케이워터운영관리(주) | 케이워터기술(주) | 합천수상태양광(주) | 합천수상태양광이차(주) | 양구수상태양광(주) | 임하수상태양광(주) | PTKarianWaterServices | JSCNenskraHydro | TinaHydropowerLimited | KDSHydroPte. Ltd. | PatrindO&amp;M(Private)Limited | PTHasangOperationandMaintenance</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0221&amp;reportFormRootNo=31901&amp;disclosureNo=2026101203251504</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>107466</v>
+        <v>29357</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>88927</v>
+        <v>30082</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국에너지기술평가원</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3720,18 +3722,18 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>29357</v>
+        <v>28177</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3748,46 +3750,44 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30082</v>
+        <v>25676</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>28177</v>
+        <v>18927</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국원산지정보원</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3804,158 +3804,168 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>25676</v>
+        <v>27748</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>한국원자력안전기술원</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>18927</v>
+        <v>28112</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>27748</v>
+        <v>18898</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
+          <t>한국원자력의학원</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>28112</v>
+        <v>31848</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>KOFPI.PARAGUAY.S.A</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>18898</v>
+        <v>29408</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>31848</v>
+        <v>486798</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3971,113 +3981,107 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
+          <t>한국잡월드파트너즈(주)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29408</v>
+        <v>29541</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>70</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>486798</v>
+        <v>18885</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전기안전공사</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>한국잡월드파트너즈(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>29541</v>
+        <v>18893</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>케이피엑스서비스원주식회사</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>18885</v>
+        <v>28110</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국전력공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4092,18 +4096,18 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>18893</v>
+        <v>34718</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4119,49 +4123,55 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>케이피엑스서비스원주식회사</t>
+          <t>한전기술서비스(주)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>28110</v>
+        <v>45471</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>한국조폐공사</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>34718</v>
+        <v>36854</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4177,30 +4187,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>45471</v>
+        <v>30024</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4209,30 +4219,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>36854</v>
+        <v>179648</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4241,30 +4251,30 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>30024</v>
+        <v>40150</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4273,62 +4283,56 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>179648</v>
+        <v>47667</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>2</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>40150</v>
+        <v>18901</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4337,176 +4341,176 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>47667</v>
+        <v>105873</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>한국청소년활동진흥원</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>키와파트너스㈜</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>18901</v>
+        <v>30152</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>105873</v>
+        <v>27771</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국탄소산업진흥원</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>30152</v>
+        <v>76710</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>27771</v>
+        <v>137012</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>76710</v>
+        <v>18886</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>한국특허기술진흥원</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4515,56 +4519,58 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+          <t>IPKoreaCenterInc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>137012</v>
+        <v>29484</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>한국해양과학기술원</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18886</v>
+        <v>47715</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4573,210 +4579,208 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>IPKoreaCenterInc</t>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>29484</v>
+        <v>649843</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>한국해외인프라도시개발지원공사</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KINDUSALLC</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>47715</v>
+        <v>67553</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>649843</v>
+        <v>74985</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>67553</v>
+        <v>18902</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>한국환경산업기술원</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>74985</v>
+        <v>29951</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>29951</v>
+        <v>25431</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>25431</v>
+        <v>40052</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한전원자력연료주식회사</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4785,55 +4789,49 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>40052</v>
+        <v>32945</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>2</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>32945</v>
+        <v>18899</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
+          <t>해양수산과학기술진흥원</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -4848,67 +4846,41 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>18899</v>
+        <v>18900</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>18900</v>
+        <v>40378</v>
       </c>
       <c r="H150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
-        <v>40378</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/subsidiary_validation_report.xlsx
+++ b/output/subsidiary_validation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,35 +957,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>아리랑TV미디어</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1402&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151760</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>28201</v>
+        <v>32028</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1001,208 +1005,208 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>아리랑TV미디어</t>
+          <t>지케이엘위드주식회사</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0031&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>32028</v>
+        <v>29465</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>극지연구소</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>지케이엘위드주식회사</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0357&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156669</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>29465</v>
+        <v>27698</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>극지연구소</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0383&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157897</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>27698</v>
+        <v>172598</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>35</v>
-      </c>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>(주)기보메이트 | (주)새연에스엔에스 | (주)아이컨택트 | (주)코아에이스 | (주)앨리스에프엑스 | (주)코베리 | (주)트로젝트 | (주)희광에너지 | 드림비전스(주) | (주)핸섬피쉬 | (주)애니닥터헬스케어 | (주)대오 | (주)쓰리케이솔루션 | (주)더마로닉 | (주)셀로긴 | (주)에스피아이(SPICO.,LTD.) | (주)엑스젠테크놀러지 | (주)시누스 | (주)퓨젼스포츠코리아 | (주)엔젤스포츠 | (주)오승이에스 | (주)에스엠하이텍 | 성민산업(주) | (주)제이에스테크 | (주)부산데이터복구서버유에스비외장하드복구데이터세이브 | (주)애드피디 | (주)로드파크 | (주)아이디어하이 | (주)우프컴퍼니 | 에스엠푸드(주) | (주)소리안 | (주)케이탑뷰티 | (주)데코데코 | (주)제이엘디앤아이 | (주)엔보이비젼</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0038&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156089</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>172598</v>
+        <v>18907</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>대구경북첨단의료산업진흥재단</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>주식회사 메디밸리파트너스</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0404&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152502</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>18907</v>
+        <v>27792</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>주식회사 메디밸리파트너스</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0894&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153399</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>27792</v>
+        <v>30073</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0054&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154251</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30073</v>
+        <v>32442</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1211,30 +1215,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(주)한몽에너지 | (유)훗고르샤나가</t>
+          <t>(주)한빛씨에스</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0057&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159070</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>32442</v>
+        <v>30985</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>독립기념관</t>
+          <t>부산항만공사</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1243,81 +1247,81 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(주)한빛씨에스</t>
+          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0065&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159448</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>30985</v>
+        <v>54784</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3</v>
-      </c>
+          <t>북한이탈주민지원재단</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>(주)부산항보안공사 | BusanPortAuthorityB.V. | B2BLOGISTICS(BUSANBARCELONAHUB), S.L.</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0072&amp;reportFormRootNo=31901&amp;disclosureNo=2026052603185963</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>54784</v>
+        <v>18892</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>분당서울대학교병원</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>이지케어텍</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0449&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>18892</v>
+        <v>35067</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1333,90 +1337,90 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>이지케어텍</t>
+          <t>티피에스주식회사</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0444&amp;reportFormRootNo=31901&amp;disclosureNo=2026062903201957</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>35067</v>
+        <v>30952</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>티피에스주식회사</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0075&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154578</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>30952</v>
+        <v>27732</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(주)국민행복기금</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>27732</v>
+        <v>27693</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1425,113 +1429,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(주)국민행복기금</t>
+          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1046&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154222</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>27693</v>
+        <v>37766</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2</v>
-      </c>
+          <t>서울대학교치과병원</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>이지케어텍(주) | (주)에스앤유에이치벤처</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0083&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155698</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>37766</v>
+        <v>18898</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>서울올림픽기념국민체육진흥공단</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0084&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159588</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>18898</v>
+        <v>50218</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한국체육산업개발(주) | 한국모태펀드(스포츠계정) | 한국스포츠레저(주)</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0029&amp;reportFormRootNo=31901&amp;disclosureNo=2026051203175331</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>50218</v>
+        <v>38441</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1548,137 +1548,141 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0905&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152886</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>38441</v>
+        <v>29495</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+          <t>식품안전정보원</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0089&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156195</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>29495</v>
+        <v>18889</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>신용보증기금</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>38</v>
+      </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0661&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155527</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>18889</v>
+        <v>165902</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>38</v>
-      </c>
+          <t>에너지경제연구원</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>신보운영관리(주) | 신보글로벌2024제2차유동화전문회사(유) | (주)햇살유통 | (주)홈디 | (주)휴 | (주)지이테크 | (주)왓스업 | 국제통신(주) | (주)쵸이스맨파워 | (주)모이어 | 우리전선(주) | (주)베스트비투비 | 한별철강(주) | (주)안온 | (주)선메트 | (주)지이티 | (주)8푸드 | (주)금양스텐 | 베스람코리아(주) | (주)파워젠 | (주)에스비하이텍 | 경기산업(주) | 지성에스이(주) | (주)씽크리에이티브 | (주)새누리 | (주)기원무역 | (주)동진 | (주)케이에스티정보통신 | (주)섬김컴퍼니 | (주)스노파 | (주)반석 | 엠티솔루션경서판매(주) | 찬우축산(주) | 일품푸드(주) | (주)엠오엠티 | 한국고벨(주) | (주)육일침장 | (주)비에프이커머스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0091&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158411</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>165902</v>
+        <v>18893</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>여수광양항만공사</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0096&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154936</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>18893</v>
+        <v>32668</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>연구개발특구진흥재단</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1687,30 +1691,30 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>여수광양항만관리(주) | 여수엑스포관리(주)</t>
+          <t>(주)연구개발특구에프엔에스</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0281&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157594</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>32668</v>
+        <v>45374</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>연구개발특구진흥재단</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1719,30 +1723,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(주)연구개발특구에프엔에스</t>
+          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0050&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157036</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>45374</v>
+        <v>58857</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1751,23 +1755,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(주)케이알앤씨 | (주)예울에프엠씨 | 서울보증보험(주) | 예별손해보험(주)</t>
+          <t>케이바이오스타트</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0101&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156657</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>58857</v>
+        <v>27695</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1783,30 +1787,30 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>케이바이오스타트</t>
+          <t>울산항만관리(주)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0896&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156925</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>27695</v>
+        <v>35742</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1815,30 +1819,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>울산항만관리(주)</t>
+          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0365&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157076</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>35742</v>
+        <v>52272</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>인천항만공사</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1847,55 +1851,49 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>인천공항시설관리(주) | 인천공항운영서비스(주) | 인천국제공항보안(주) | 인천공항에너지(주) | PT. MitraIncheonIndonesia | IncheonKoreaforAirportServicesCompanyS.P.C | IncheonAirportPhilippinesCorporation</t>
+          <t>인천항보안공사</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0105&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154572</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>52272</v>
+        <v>29463</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
+          <t>재단법인 대한건설기계안전관리원</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>인천항보안공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0107&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156285</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>29463</v>
+        <v>18918</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1910,158 +1908,164 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1108&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155008</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>18918</v>
+        <v>18902</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>정보통신기획평가원</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0553&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154771</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>18902</v>
+        <v>25446</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+          <t>정보통신정책연구원</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0908&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152505</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>25446</v>
+        <v>18888</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>제주국제자유도시개발센터</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0120&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156295</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>18888</v>
+        <v>43081</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>주식회사 에스알</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(주)제인스 | 제이디씨예래리조트(주) | 제이디씨파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0121&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155481</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>43081</v>
+        <v>28134</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>주식회사 에스알</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1044&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153908</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>28134</v>
+        <v>220531</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>중소기업은행</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2077,30 +2081,30 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(주)도시재생앵커제1호위탁관리부동산투자회사 | (주)산단재생1호서대구지식산업센터위탁관리부동산투자회사 | (주)서울창동창업문화도시재생위탁관리부동산투자회사 | ㈜엔에이치에프제1호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제2호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제3호공공임대위탁관리부동산투자회사 | ㈜펨코제7호민간임대주택위탁관리부동산투자회사 | ㈜인천도화위탁관리부동산투자회사 | ㈜엔에이치에프제4호공공임대위탁관리부동산투자회사 | ㈜인천도화뉴스테이기업형임대위탁관리부동산투자회사 | ㈜인천도화공공임대위탁관리부동산투자회사 | ㈜해피투게더스테이제1호위탁관리부동산투자회사 | ㈜하나스테이제1호위탁관리부동산투자회사 | ㈜우리천안두정위탁관리부동산투자회사 | ㈜엔에이치에프제5호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제6호공공임대위탁관리부동산투자회사 | ㈜대한제1호뉴스테이위탁관리부동산투자회사 | ㈜동탄2대우코크렙뉴스테이기업형임대위탁관리부동산투자회사 | ㈜예미지뉴스테이기업형임대위탁관리부동산투자회사 | ㈜위례뉴스테이기업형임대위탁관리부동산투자회사 | ㈜뉴스테이허브제1호위탁관리부동산투자회사 | ㈜엔에이치에프제7호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제8호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제9호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제10호공공임대위탁관리부동산투자회사 | ㈜뉴스테이허브제2호위탁관리부동산투자회사 | ㈜뉴스테이허브제3호위탁관리부동산투자회사 | ㈜엔에이치에프제11호공공임대위탁관리부동산투자회사 | ㈜청년희망임대주택위탁관리부동산투자회사 | ㈜국민행복주택제1호위탁관리부동산투자회사 | ㈜엔에이치에프제12호공공임대위탁관리부동산투자회사 | ㈜서울리츠임대주택제1호위탁관리부동산투자회사 | ㈜민간임대허브제4호위탁관리부동산투자회사 | ㈜엔에이치에프제13호공공임대위탁관리부동산투자회사 | ㈜엔에이치에프제14호공공임대위탁관리부동산투자회사 | ㈜민간임대허브제5호위탁관리부동산투자회사 | ㈜엔에이치에프제15호공공임대위탁관리부동산투자회사 | ㈜국민행복주택제2호위탁관리부동산투자회사 | ㈜ 엔에이치에프제16호공공임대위탁관리부동산투자회사 | ㈜ 경기리츠공공임대제1호위탁관리부동산투자회사 | ㈜토지지원리츠제2호위탁관리부동산투자회사 | ㈜서울사회주택토지지원위탁관리부동산투자회사 | ㈜민간임대허브제6호위탁관리부동산투자회사 | ㈜민간임대허브제7호위탁관리부동산투자회사 | ㈜민간임대허브제8호위탁관리부동산투자회사 | 한국토지주택공사(주택도시기금) | 주택도시보증공사(주택도시기금) | (주)코람코주택도시기금위탁관리부동산투자회사</t>
+          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0061&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172810</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>220531</v>
+        <v>253990</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>중소기업은행</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2109,113 +2113,109 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>㈜IBK캐피탈 | IBK투자증권㈜ | IBK연금보험㈜ | IBK자산운용㈜ | ㈜IBK저축은행 | ㈜IBK벤처투자 | ㈜IBK시스템 | IBK신용정보㈜ | ㈜IBK서비스 | 기업은행(중국)유한공사 | IBK인도네시아은행 | IBK미얀마은행 | IBK폴란드은행 | ㈜조흥포장 | ㈜에이팸 | ㈜페타미디어 | ㈜코시트 | 주식회사 에버조이 | 브랜드케이청년창조기술금융사모투자합자회사 | 아이비케이케이아이피성장디딤돌제1호사모투자합자회사 | 아이비케이포스코트루벤기업재무안정사모투자전문회사 | 아이비케이티에스엑시트제2호사모투자합자회사 | 아이비케이비엔더블유기술금융2018사모투자합자회사 | 아이비케이스톤브릿지혁신성장사모투자합자회사 | 기술금융제일호사모투자전문회사 | 아이비케이비엔더블유산업경쟁력성장지원사모투자합자회사 | 아이비케이스톤브릿지뉴딜이에스지유니콘사모투자합자회사 | 아이비케이키움사업재편사모투자합자회사 | 아이비케이엘엑스지스케일업수출지원사모투자합자회사 | 아이비케이한국투자성장사다리사모투자합자회사 | 아이비케이키움중소중견점프업사모투자합자회사 | 피씨씨-베일리프로젝트투자조합 | IBK창공비상1호투자조합 | IBK금융그룹미래성장동력투자조합 | IBK금융그룹크라우드펀딩매칭투자조합 | IBK금융그룹창업기업일자리창출투자조합 | 비전소재부품장비벤처투자조합제1호((주)리비콘에대한투자) | IBK창공비상2호투자조합 | IBK-스톤브릿지라이징2호투자조합 | 500코리아III투자조합 | 허니팟HGI뉴투자조합 | 스타트업코리아IBKVC-코오롱2024펀드 | 스타트업코리아IBKVC-FP2024펀드 | 앨리스-하나에스앤비소부장신기술투자조합 | 헬리오스테이아벤처투자조합제1호 | 2024딥다이브파트너스사모투자합자회사 | 아이비케이금융그룹창공1호투자조합 | 2025IBKVC-대신넥스트밸류업펀드</t>
+          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0127&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155486</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>253990</v>
+        <v>79799</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>5</v>
-      </c>
+          <t>충남대학교병원</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>(주)한국중소벤처기업유통원 | 한국벤처투자 | (주)중소벤처기업인증원 | 중진공파트너스(주) | 엔에스엘이디(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0130&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155972</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>79799</v>
+        <v>18894</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>코레일네트웍스(주)</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>(주)케이아이비보험중개</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0135&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153634</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>18894</v>
+        <v>39615</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>코레일유통(주)</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>(주)케이아이비보험중개</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0327&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154138</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>39615</v>
+        <v>59337</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코레일유통(주)</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2232,53 +2232,57 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0272&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153245</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>59337</v>
+        <v>29361</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>태권도원운영관리(주)</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0387&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155618</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>29361</v>
+        <v>27791</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2287,116 +2291,116 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>태권도원운영관리(주)</t>
+          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0409&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>27791</v>
+        <v>125894</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>한국개발연구원</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>(주)한국가스기술공사 | 케이씨엘엔지테크(주) | KOGASInternationalPte. Ltd. | KoreaRasLaffanLNGLtd.(주1) | KGKruengManeLtd. | KOGASCyprusLtd. | KGMozambiqueLtd. | KOMEX-GAS, S. deR. L. deC.V.(주3) | KOGAMEXInvestmentManzanilloB.V. | KOGASIraqB.V. | KOGASBadraB.V. | KOGASMansuriyaB.V. | KOGASAkkasB.V. | KOGASAustraliaPty. Ltd. | KOGASPreludePty. Ltd. | KOGASMozambiqueLda. | KG-SEAGPCompanyLimited | KOGASCanadaEnergyLtd. | 한국엘엔지벙커링주식회사 | 코가스서비스얼라이언스(주)(주6) | 코가스보안관리(주)(주6)</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0147&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156631</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>125894</v>
+        <v>27746</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>한국개발연구원</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+          <t>한국고용정보원</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0151&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159265</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>27746</v>
+        <v>18882</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>한국공항공사</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0321&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153525</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>18882</v>
+        <v>44938</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2405,143 +2409,143 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>케이에이씨공항서비스주식회사 | 남부공항서비스주식회사 | 한국공항보안주식회사 | 김포공항및주변지역개발사업주식회사</t>
+          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0157&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155238</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>44938</v>
+        <v>41897</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>그랜드코리아레저(주) | 케이티오파트너스(주)</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0165&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154165</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>41897</v>
+        <v>27701</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국관세정보원</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1400&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155439</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>27701</v>
+        <v>88689</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>KoresAustraliaPtyLtd | KORESCANADACorp. | ErmaniLtd. | KoreanBoleoCorp | 코미르엠지엘유한회사</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1364&amp;reportFormRootNo=31901&amp;disclosureNo=2026042903170004</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>88689</v>
+        <v>28120</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>(주)코웍스</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0019&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152114</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>28120</v>
+        <v>29465</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2557,30 +2561,30 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(주)코웍스</t>
+          <t>엘엑스파트너스(주)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0146&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153449</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>29465</v>
+        <v>33176</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2589,30 +2593,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>엘엑스파트너스(주)</t>
+          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153964</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>33176</v>
+        <v>134228</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C75" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2621,88 +2625,88 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KOSEPAustraliaPty.,Ltd. | MiraPowerLimited | ㈜에스이그린에너지 | 코셉머티리얼㈜ | 탐라해상풍력발전㈜ | KOENBylongPty., Ltd. | PT. koreaEnergyIndonesia | KOLATSpA | ㈜ 코엔서비스 | KOAKPowerLimited | ㈜케이솔라신안 | 코엔바이오㈜ | KAPowerLimited | ASM-BGInvesticiiAD | RESTechnologyAD | NepalWater&amp;EnergyDevelopmentCompanyPty.,Ltd. | 고속도로태양광발전㈜</t>
+          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0042&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153576</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>134228</v>
+        <v>143256</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>9</v>
-      </c>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>KOSPOAustraliaPty., Ltd. | KOSPOJORDANL.L.C. | KOSPOChileSpA | KOSPOBylongPty., Ltd. | KOSPOUSAInc. | 코스포영남파워(주) | 코스포서비스(주) | 정암풍력발전(주) | 창죽풍력발전(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0043&amp;reportFormRootNo=31901&amp;disclosureNo=2026082003231587</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>143256</v>
+        <v>18904</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>한국농수산식품유통공사</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>에이플(주) | 칭다오aT물류유한공사</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0378&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152680</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>18904</v>
+        <v>40886</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국농어촌공사</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2711,30 +2715,30 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>에이플(주) | 칭다오aT물류유한공사</t>
+          <t>KRCThailand. Co.Ltd</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0045&amp;reportFormRootNo=31901&amp;disclosureNo=2026052103184405</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>40886</v>
+        <v>43163</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2743,30 +2747,30 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KRCThailand. Co.Ltd</t>
+          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0046&amp;reportFormRootNo=31901&amp;disclosureNo=2026070903208997</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>43163</v>
+        <v>59121</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2775,30 +2779,30 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>부산울산고속도로 | 한국도로공사시설관리 | 한국도로공사서비스</t>
+          <t>도로교통안전관리주식회사</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0183&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177933</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>59121</v>
+        <v>35354</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2807,30 +2811,30 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>도로교통안전관리주식회사</t>
+          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0064&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156524</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>35354</v>
+        <v>120832</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국디자인진흥원</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2839,81 +2843,81 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EWPAmerica, Inc. | EWP(Barbados)1SRL | PT. EWPIndonesia | 경주풍력발전(주) | EWPBylongPtyLimited | 이더블유피서비스(주) | 파주에코에너지(주) | 영덕해맞이풍력(주) | EWPAustraliaPtyLtd</t>
+          <t>베이징KIDP산업디자인서비스유한공사</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0066&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157627</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>120832</v>
+        <v>28662</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국디자인진흥원</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>베이징KIDP산업디자인서비스유한공사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0184&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152474</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>28662</v>
+        <v>18900</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>한국마사회</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한국마사회시설관리(주)</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0450&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152827</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>18900</v>
+        <v>33122</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국마사회</t>
+          <t>한국무역보험공사</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2929,23 +2933,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>한국마사회시설관리(주)</t>
+          <t>주식회사 신아에스비(SLS조선)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0185&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154007</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>33122</v>
+        <v>54975</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국무역보험공사</t>
+          <t>한국문화예술위원회</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2961,23 +2965,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>주식회사 신아에스비(SLS조선)</t>
+          <t>한국문화진흥(주)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0222&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156747</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>54975</v>
+        <v>29390</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국문화예술위원회</t>
+          <t>한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2993,90 +2997,90 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>한국문화진흥(주)</t>
+          <t>코바코파트너스주식회사</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0190&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157767</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>29390</v>
+        <v>29945</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국방송통신전파진흥원</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>코바코파트너스주식회사</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0196&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159012</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>29945</v>
+        <v>40112</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0187&amp;reportFormRootNo=31901&amp;disclosureNo=2026051103174398</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>40112</v>
+        <v>44776</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국보건산업진흥원</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3085,90 +3089,90 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KVICSILICONVALLEYInc | KVICASIAPTELTD</t>
+          <t>코리아메디컬홀딩스</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0199&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153797</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>44776</v>
+        <v>27749</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국보건산업진흥원</t>
+          <t>한국보훈복지의료공단</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>코리아메디컬홀딩스</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0201&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156893</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>27749</v>
+        <v>28489</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국보훈복지의료공단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>알이비파트너스주식회사</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0203&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153655</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>28489</v>
+        <v>37302</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3177,266 +3181,266 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>알이비파트너스주식회사</t>
+          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0150&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153457</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>37302</v>
+        <v>284523</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>39</v>
-      </c>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>에듀이십일건국대기숙사유한회사 | 경북글로벌교류센터유한회사 | 익산글로벌교류센터유한회사 | 강릉영동대학교행복기숙사유한회사 | 경희대학교서울캠퍼스행복기숙사유한회사 | 고신대학교행복기숙사유한회사 | 광운대학교행복기숙사유한회사 | 나사렛대학교행복기숙사유한회사 | 단국대학교행복기숙사유한회사 | 대경대학교행복기숙사유한회사 | 대구한의대학교행복기숙사유한회사 | 상명대학교행복기숙사유한회사 | 서영대학교행복기숙사유한회사 | 성공회대학교행복기숙사유한회사 | 세종대학교행복기숙사유한회사 | 송원대학교행복기숙사유한회사 | 수성대학교행복기숙사유한회사 | 신한대학교의정부캠퍼스행복기숙사유한회사 | 영남이공대학교행복기숙사유한회사 | 원광보건대학교행복기숙사유한회사 | 전주비전대학교행복기숙사유한회사 | 제주관광대학교행복기숙사유한회사 | 충북보건과학대학교행복기숙사유한회사 | 한국국제대학교행복기숙사유한회사 | 한동대학교행복기숙사유한회사 | 한성대학교행복기숙사유한회사 | 한양대학교행복기숙사유한회사 | 대전보건대학교행복기숙사유한회사 | 호서대학교행복기숙사유한회사 | 경희대학교국제캠퍼스학생기숙사유한회사 | 한국사학진흥재단행복기숙사유한회사 | 극동대학교행복기숙사유한회사 | 상지대학교행복기숙사유한회사 | 대진대학교행복기숙사유한회사 | 동남보건대학교행복기숙사유한회사 | 경인여자대학교행복기숙사유한회사 | 용인대학교행복기숙사유한회사 | 인하대학교행복기숙사유한회사 | 아주대학교행복기숙사유한회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0205&amp;reportFormRootNo=31901&amp;disclosureNo=2026071303214610</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>284523</v>
+        <v>18899</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>한국산림복지진흥원</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>(주)포이파트너스</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0456&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155154</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>18899</v>
+        <v>33086</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국산업기술기획평가원</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>(주)포이파트너스</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1055&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159539</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>33086</v>
+        <v>25488</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>KTLChinaCo.,Ltd</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0397&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153560</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>25488</v>
+        <v>29432</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>KTLChinaCo.,Ltd</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0076&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153077</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>29432</v>
+        <v>95628</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(주)키콕스파트너스</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0393&amp;reportFormRootNo=31901&amp;disclosureNo=2026050703172807</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>95628</v>
+        <v>45152</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>(주)키콕스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0208&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157478</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>45152</v>
+        <v>18918</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>한국산업은행</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>48</v>
+      </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0209&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156381</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>18918</v>
+        <v>250565</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C102" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3445,30 +3449,30 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>산은인프라자산운용(주) | 산은인베스트먼트(주) | 산은비즈(주) | 산은캐피탈(주) | 기업유동성지원기구 | 한국교육투융자회사(주) | 한국비티엘일호투융자회사 | 한국철도일호투융자회사 | KDBSILICONVALLEYLLC | BANCOKDBDOBRASILS.A. | PTKDBTIFAFINANCETBK | JSCKDBBANKUZBEKISTAN | KDBIRELANDDESIGNATEDACTIVITYCOMPANY | KDBBANKEUROPELIMITED | KDBASIALIMITED | 케이디비생명보험(주) | 케이디비중소중견메자닌사모투자합자회사 | 케이디비아이에이피일대일로사모투자합자회사 | 케이디비아시아사모투자합자회사 | 케이디비칸서스밸류사모투자전문회사 | 그린이니셔티브2호사모투자합자회사 | 호주그린에너지제1호사모투자합자회사 | 케이디비케이엘중소중견밸류업제2호사모투자(자) | KDBSynergy, L.P. | KDBOCCASIOII, L.P. | KDBC공동투자사모투자합자회사 | 아이비케이에스중소기업도약사모투자합자회사 | 스마일게이트소재부품투자펀드2014-3호 | DKIGrowingStar3호투자조합 | SLI소재부품투자펀드2014-1호 | 페트라6의1호사모투자합자회사 | 엔베스터창해유주사모투자합자회사 | KoFC-KVIC일자리창출펀드2호 | 플래티넘-유망산업펀드 | 엔에이치엘비그로쓰챔프2011의4호사모투자전문회사합자회사 | 아세안바이오메디컬투자조합 | 케이디비아이하나사업재편밸류업사모투자합자회사 | 유안타세컨더리2호펀드 | 하나제삼호사모투자합자회사 | 원익그로쓰챔프2011의3호사모투자전문회사합자회사 | 알바트로스퓨처코리아투자조합 | 블루오션기업재무안정제1호사모투자전문회사합자회사 | 충청권글로벌기술투자조합 | KoFC-BKPioneerChamp2010-13호투자조합 | 웨일제1호중소중견기업엠앤에이사모투자합자회사 | DSC유망서비스산업펀드 | 와이제이에이중소중견기업엠앤에이사모투자합자회사 | 케이디비대성-HGI그린임팩트투자조합</t>
+          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0210&amp;reportFormRootNo=31901&amp;disclosureNo=2026091603242430</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>250565</v>
+        <v>136051</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국석유공사</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3477,48 +3481,44 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KOWEPOInternationalCorporation | KOWEPOAustraliaPty.,Ltd. | KOWEPOLaoInternational | KOWEPOBylongPty.,Ltd | 코웨포서비스(주) | 한강해나눔서부발전에너지전문투자형사모특별자산투자신탁(해나눔에너지펀드) | KOWEPOEuropeB.V. | 서부발전창기태양광(주)(구,삼양태양광(주)) | KOWEPOHoldingLimited</t>
+          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0082&amp;reportFormRootNo=31901&amp;disclosureNo=2026041503161674</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>136051</v>
+        <v>110552</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>한국세라믹기술원</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>ANKORE&amp;PHoldingsCorp. | DanaPetroleumLtd. | KNOCEaglefordCorp. | HarvestOperationsCorp | KNOCKazB.V. | KNOCSumatraLtd. | KNOCYemenLtd. | KNOCNigerianWestOilCompanyLtd. | KNOCNigerianEastOilCompanyLtd. | KADOCLtd. | 동해부유식해상풍력발전㈜ | 코리아에너지터미널(주) | KNOCTradingSingapore.Pte.Ltd | 케이엔오씨서비스(주)</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0214&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152097</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>110552</v>
+        <v>58851</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3528,25 +3528,23 @@
           <t>한국소방산업기술원</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0103&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154641</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0217&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157755</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>58851</v>
+        <v>18898</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3617,39 +3615,35 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>수은영국은행 | 수은아주금융유한공사 | 수은인니금융 | 수은베트남리스금융회사 | 수은싱가포르 | 수은플러스(주)</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0223&amp;reportFormRootNo=31901&amp;disclosureNo=2026071003213995</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>88927</v>
+        <v>29357</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3666,18 +3660,18 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0335&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156582</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>29357</v>
+        <v>30082</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>한국에너지기술평가원</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3694,18 +3688,18 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0097&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154234</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>30082</v>
+        <v>28177</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국에너지기술평가원</t>
+          <t>한국연구재단</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3722,193 +3716,197 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0389&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156339</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>28177</v>
+        <v>25676</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0388&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158320</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>25676</v>
+        <v>18927</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>한국원산지정보원</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0849&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159333</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>18927</v>
+        <v>27748</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
+          <t>한국원자력안전기술원</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(주)킨스파트너스</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0916&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303151856</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>27748</v>
+        <v>28112</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(주)킨스파트너스</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0234&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156231</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>28112</v>
+        <v>18898</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>한국원자력의학원</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0932&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158190</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>18898</v>
+        <v>31848</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>KOFPI.PARAGUAY.S.A</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0104&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153101</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>31848</v>
+        <v>29408</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3917,30 +3915,30 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KOFPI.PARAGUAY.S.A</t>
+          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0857&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154400</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>29408</v>
+        <v>486798</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3949,55 +3947,49 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>㈜캠코씨에스 | ㈜캠코에프엠씨 | 캠코동산금융지원㈜ | 캠코기업지원금융㈜ | 캠코선박운용㈜ | 이에이에스제오차유동화전문유한회사 | 기업구조혁신사모투자합자회사4호 | 기업구조혁신재정사모투자합자회사5호 | 기업구조혁신정책사모투자합자회사5호 | 기업구조혁신재정사모투자합자회사6호 | 기업구조혁신정책사모투자합자회사6호 | 온기업1호기업재무안정사모투자합자회사 | 노앤자원순환제1호사모투자합자회사 | 인비전사모투자합자회사 | ㈜케이원제16호분당위탁관리부동산투자회사 | ㈜하나트러스트제8호위탁관리부동산투자회사 | ㈜에이치엘제2호위탁관리부동산투자회사 | ㈜에이치엘제5호위탁관리부동산투자회사 | 한국토니지14호선박투자회사 | 한국토니지30호선박투자회사 | 한국토니지31호선박투자회사 | 한국토니지32호선박투자회사 | 한국토니지33호선박투자회사 | 한국토니지34호선박투자회사 | 한국토니지35호선박투자회사 | 한국토니지46호선박투자회사 | 한국토니지47호선박투자회사 | 한국토니지55호선박투자회사 | 한국토니지57호선박투자회사 | 한국토니지62호선박투자회사 | 한국토니지65호선박투자회사 | 한국토니지68호선박투자회사 | 한국토니지69호선박투자회사 | 한국토니지75호선박투자회사 | 한국토니지76호선박투자회사 | 한국토니지77호선박투자회사 | 한국토니지78호선박투자회사 | 한국토니지79호선박투자회사 | 한국토니지81호선박투자회사 | 한국토니지82호선박투자회사 | 한국토니지83호선박투자회사 | 한국토니지88호선박투자회사 | 한국토니지89호선박투자회사 | 한국토니지90호선박투자회사 | 한국토니지91호선박투자회사 | 한국토니지92호선박투자회사 | 한국토니지93호선박투자회사 | 한국토니지94호선박투자회사 | 한국토니지102호선박투자회사 | 한국토니지103호선박투자회사 | 한국토니지105호선박투자회사 | 한국토니지106호선박투자회사 | 한국토니지107호선박투자회사 | 한국토니지108호선박투자회사 | 한국토니지109호선박투자회사 | 한국토니지110호선박투자회사 | 한국토니지111호선박투자회사 | 한국토니지112호선박투자회사 | 한국토니지113호선박투자회사 | 한국토니지114호선박투자회사 | 한국토니지115호선박투자회사 | 한국토니지116호선박투자회사 | 한국토니지117호선박투자회사 | 한국토니지118호선박투자회사 | 한국토니지119호선박투자회사 | 한국토니지120호선박투자회사 | 한국토니지신조7호선박투자회사 | 한국토니지신조8호선박투자회사 | 한국토니지신조9호선박투자회사 | 한국토니지신조10호선박투자회사</t>
+          <t>한국잡월드파트너즈(주)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0240&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154559</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>486798</v>
+        <v>29541</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1</v>
-      </c>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>한국잡월드파트너즈(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0859&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156499</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>29541</v>
+        <v>18885</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
+          <t>한국전기안전공사</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4012,109 +4004,115 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0243&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159205</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>18885</v>
+        <v>18893</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>케이피엑스서비스원주식회사</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0244&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156268</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>18893</v>
+        <v>28110</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>케이피엑스서비스원주식회사</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0246&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157903</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>28110</v>
+        <v>34718</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>한국전력기술주식회사</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>한전기술서비스(주)</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0247&amp;reportFormRootNo=31901&amp;disclosureNo=2026051503177483</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>34718</v>
+        <v>45471</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4123,30 +4121,30 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>한전기술서비스(주)</t>
+          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0248&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153137</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>45471</v>
+        <v>36854</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국주택금융공사</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4155,30 +4153,30 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>GLOBALKOMSCODAEWOOLLC. | ㈜콤스코투게더 | ㈜콤스코시큐리티</t>
+          <t>에이치에프파트너스주식회사</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0257&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155248</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>36854</v>
+        <v>30024</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4187,30 +4185,30 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>에이치에프파트너스주식회사</t>
+          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0258&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153832</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>30024</v>
+        <v>179648</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4219,30 +4217,30 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KOMIPOGlobalPteLtd. | KOMIPOAustraliaPtyLtd. | PT. KOMIPOPembangkitanJawaBali | KOMIPOAmericaInc. | KOMIPOBylongPtyLtd | PT. KOMIPOEnergyIndonesia | 중부발전서비스㈜ | KOMIPOEuropeB.V. | KOMIPOVanPhongPowerServiceLLC | 오기리태양광발전㈜</t>
+          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0259&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155494</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>179648</v>
+        <v>40150</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4251,88 +4249,88 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑 | 한유원파트너스(주)</t>
+          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0126&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155034</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>40150</v>
+        <v>47667</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>3</v>
-      </c>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>한국지역난방기술(주) | 지역난방안전(주) | 지역난방플러스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0261&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303153395</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>47667</v>
+        <v>18901</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>한국철도공사</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>5</v>
+      </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0264&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155561</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>18901</v>
+        <v>105873</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국청소년활동진흥원</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4341,55 +4339,51 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>코레일유통㈜ | 코레일네트웍스㈜ | 코레일로지스㈜ | 코레일관광개발㈜ | 코레일테크㈜</t>
+          <t>키와파트너스㈜</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0268&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152379</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>105873</v>
+        <v>30152</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국콘텐츠진흥원</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>키와파트너스㈜</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0447&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155921</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>30152</v>
+        <v>27771</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>한국탄소산업진흥원</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -4406,171 +4400,175 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0395&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303159111</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>27771</v>
+        <v>76710</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
+          <t>한국토지주택공사</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1368&amp;reportFormRootNo=31901&amp;disclosureNo=2026092903246649</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>76710</v>
+        <v>137012</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>5</v>
-      </c>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>주택관리공단(주) | 엘에이치주거복지정보(주) | (주)엘에이치이앤에스 | 한누리(주) | LHPRIMORYE, LLC</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0396&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152971</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>137012</v>
+        <v>18886</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>한국특허기술진흥원</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>IPKoreaCenterInc</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0284&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303158465</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>18886</v>
+        <v>29484</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국특허기술진흥원</t>
+          <t>한국해양과학기술원</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>IPKoreaCenterInc</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0858&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156088</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>29484</v>
+        <v>47715</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0297&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156424</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>47715</v>
+        <v>649843</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국해외인프라도시개발지원공사</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4579,176 +4577,176 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>KOBCCONTAINERLEASINGNO. 1LIMITED | KOBCCONTAINERLEASINGNO. 2LIMITED | KOBCCONTAINERLEASINGNO. 3LIMITED | KOBCUSALLC | 국제28호선박투자회사 | 국제34호선박투자회사 | 국제35호선박투자회사 | 국제37호선박투자회사 | 국제41호선박투자회사 | 국제43호선박투자회사 | 국제44호선박투자회사 | 국제45호선박투자회사 | 국제46호선박투자회사 | 국제47호선박투자회사 | 국제49호선박투자회사 | 에스비케이엘지엘사모투자합자회사 | 에스비케이와스카사모투자합자회사 | 지엠에프구호선박투자회사 | 지엠에프비비씨이호선박투자회사 | 지엠에프비비씨일호선박투자회사 | 지엠에프삼호선박투자회사 | 지엠에프십구호선박투자회사 | 지엠에프십사호선박투자회사 | 지엠에프십삼호선박투자회사 | 지엠에프십오호선박투자회사 | 지엠에프십육호선박투자회사 | 지엠에프십이호선박투자회사 | 지엠에프십일호선박투자회사 | 지엠에프십칠호선박투자회사 | 지엠에프십팔호선박투자회사 | 지엠에프십호선박투자회사 | 지엠에프육호선박투자회사 | 지엠에프이십사호선박투자회사 | 지엠에프이십삼호선박투자회사 | 지엠에프이십육호선박투자회사 | 지엠에프이십이호선박투자회사 | 지엠에프이십일호선박투자회사 | 지엠에프이십칠호선박투자회사 | 지엠에프이십호선박투자회사 | 지엠에프이호선박투자회사 | 지엠에프일호선박투자회사 | 지엠에프칠호선박투자회사 | 케이에스에프10호선박투자회사 | 케이에스에프11호선박투자회사 | 케이에스에프12호선박투자회사 | 케이에스에프17호선박투자회사 | 케이에스에프19호선박투자회사 | 케이에스에프1호선박투자회사 | 케이에스에프20호선박투자회사 | 케이에스에프22호선박투자회사 | 케이에스에프23호선박투자회사 | 케이에스에프24호선박투자회사 | 케이에스에프26호선박투자회사 | 케이에스에프27호선박투자회사 | 케이에스에프28호선박투자회사 | 케이에스에프29호선박투자회사 | 케이에스에프2호선박투자회사 | 케이에스에프30호선박투자회사 | 케이에스에프31호선박투자회사 | 케이에스에프32호선박투자회사 | 케이에스에프33호선박투자회사 | 케이에스에프34호선박투자회사 | 케이에스에프35호선박투자회사 | 케이에스에프36호선박투자회사 | 케이에스에프37호선박투자회사 | 케이에스에프38호선박투자회사 | 케이에스에프39호선박투자회사 | 케이에스에프40호선박투자회사 | 케이에스에프41호선박투자회사 | 케이에스에프42호선박투자회사 | 케이에스에프43호선박투자회사 | 케이에스에프8호선박투자회사 | 한국선박글로벌1호선박투자회사 | 한국선박글로벌2호선박투자회사 | 한국선박글로벌4호선박투자회사 | 한국해양11호선박투자회사 | 한국해양12호선박투자회사 | 한국해양14호선박투자회사 | 한국해양16호선박투자회사 | 한국해양20호선박투자회사 | 한국해양30호선박투자회사 | 한국해양31호선박투자회사 | 한국해양34호선박투자회사 | 한국해양35호선박투자회사 | 한국해양36호선박투자회사 | 한국해양38호선박투자회사 | 한국해양40호선박투자회사 | 한국해양41호선박투자회사 | 한국해양진흥1호선박투자회사 | 한국해양진흥2호선박투자회사 | 한국해양진흥3호선박투자회사 | 해양신조1호선박투자회사 | 해양신조2호선박투자회사</t>
+          <t>KINDUSALLC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1119&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155362</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>649843</v>
+        <v>67553</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
+          <t>한국환경공단</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>KINDUSALLC</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1131&amp;reportFormRootNo=31901&amp;disclosureNo=2026061903198252</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>67553</v>
+        <v>74985</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_SUBSIDIARY_ROWS</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0400&amp;reportFormRootNo=31901&amp;disclosureNo=2026073103222879</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>74985</v>
+        <v>18902</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>북경한능환보기술자문유한공사</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C1062&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152895</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>18902</v>
+        <v>29951</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국환경산업기술원</t>
+          <t>한전KDN</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>북경한능환보기술자문유한공사</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0391&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303154574</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>29951</v>
+        <v>25431</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0306&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155122</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>25431</v>
+        <v>40052</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한전원자력연료주식회사</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4757,55 +4755,49 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KEPCOKPSPhilippinesCorp. | 케이피에스파트너스㈜ | KEPCOKPSSouthAfricaPty., Ltd.</t>
+          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0305&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152437</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>40052</v>
+        <v>32945</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>2</v>
-      </c>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>KNFCanadaEnergyLtd. | 케이앤에프파트너스(주)</t>
-        </is>
-      </c>
+          <t>NO_SUBSIDIARY_ROWS</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0236&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303152814</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>32945</v>
+        <v>18899</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
+          <t>해양수산과학기술진흥원</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -4820,67 +4812,41 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0900&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303157518</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>18899</v>
+        <v>18900</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NO_SUBSIDIARY_ROWS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0374&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303156322</t>
+          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>18900</v>
+        <v>40378</v>
       </c>
       <c r="H149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>https://www.alio.go.kr/item/itemReportTerm.do?apbaId=C0533&amp;reportFormRootNo=31901&amp;disclosureNo=2026041303155304</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
-        <v>40378</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
